--- a/docs/requirements/requirements.xlsx
+++ b/docs/requirements/requirements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SON\Desktop\관통프로젝트\project\docs\requirements\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Desktop\관통\13-pjt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F16F3F-4B91-4DF7-A7A3-3402F4C3AFAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B45811F7-0BD6-4702-AE34-5669E60DCD86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="2" xr2:uid="{6555F27F-E6EB-4F45-8CBA-89F03A0C9748}"/>
+    <workbookView xWindow="510" yWindow="1575" windowWidth="35655" windowHeight="19140" activeTab="1" xr2:uid="{6555F27F-E6EB-4F45-8CBA-89F03A0C9748}"/>
   </bookViews>
   <sheets>
     <sheet name="기능요약" sheetId="3" r:id="rId1"/>
@@ -25,12 +25,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="370">
   <si>
     <t>기능명세서</t>
   </si>
@@ -1120,9 +1123,6 @@
     <t>사용자는 선택한 은행 또는 추천된 예적금 상품과 관련된 은행 지점 위치를 지도에서 확인하고 가까운 지점을 찾을 수 있다.</t>
   </si>
   <si>
-    <t>성향 질문 응답, 결과 분석, 주거래은행 추천</t>
-  </si>
-  <si>
     <t>사용자는 MBTI 검사처럼 금융 이용 성향 질문에 답변하고, 응답 결과를 바탕으로 자신에게 적합한 주거래은행을 추천받을 수 있다.</t>
   </si>
   <si>
@@ -1149,6 +1149,41 @@
   </si>
   <si>
     <t>LLM을 활용한 금융용어 설명, 금융상품 쉬운 설명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주연</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>변경예정일</t>
+  </si>
+  <si>
+    <t>실제완료일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>업무 담당자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예정완료일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3순위</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>선택 구현</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1156,6 +1191,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="180" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
+  </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1209,7 +1247,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1219,6 +1257,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1237,7 +1281,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1262,9 +1306,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1276,6 +1317,18 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1591,18 +1644,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20E33896-2AF1-4A9F-834E-D1592E9F7F1A}">
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.19921875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="15.69921875" customWidth="1"/>
-    <col min="3" max="3" width="52.296875" customWidth="1"/>
-    <col min="4" max="4" width="53.19921875" customWidth="1"/>
-    <col min="5" max="6" width="15.69921875" customWidth="1"/>
-    <col min="7" max="7" width="29.69921875" customWidth="1"/>
+    <col min="1" max="1" width="6.25" style="2" customWidth="1"/>
+    <col min="2" max="2" width="15.75" customWidth="1"/>
+    <col min="3" max="3" width="52.25" customWidth="1"/>
+    <col min="4" max="4" width="53.25" customWidth="1"/>
+    <col min="5" max="6" width="15.75" customWidth="1"/>
+    <col min="7" max="7" width="29.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.8" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
@@ -1625,7 +1678,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1648,7 +1701,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1671,7 +1724,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1694,7 +1747,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1717,7 +1770,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1740,7 +1793,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1763,7 +1816,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -1786,7 +1839,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -1809,41 +1862,41 @@
         <v>210</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>220</v>
+        <v>36</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>353</v>
+        <v>211</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>354</v>
+        <v>212</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="G10" s="5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <v>11</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="3">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>211</v>
-      </c>
       <c r="D11" s="5" t="s">
-        <v>212</v>
+        <v>359</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>206</v>
@@ -1852,88 +1905,79 @@
         <v>207</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>132</v>
+        <v>218</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>356</v>
+        <v>219</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>360</v>
+        <v>117</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="3">
-        <v>12</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>219</v>
-      </c>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="D13" s="5" t="s">
-        <v>117</v>
+        <v>353</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>208</v>
+        <v>368</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>209</v>
+        <v>369</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C14" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="33" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="C18" s="5" t="s">
         <v>216</v>
       </c>
     </row>
@@ -1949,90 +1993,92 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O49"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:S1048576"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.69921875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="10.296875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.75" style="2" customWidth="1"/>
+    <col min="2" max="2" width="10.25" style="2" customWidth="1"/>
     <col min="3" max="3" width="10.5" customWidth="1"/>
-    <col min="4" max="4" width="10.3984375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.69921875" customWidth="1"/>
-    <col min="6" max="6" width="23.296875" customWidth="1"/>
-    <col min="7" max="7" width="42.59765625" customWidth="1"/>
-    <col min="8" max="8" width="5.8984375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="34.796875" customWidth="1"/>
-    <col min="10" max="14" width="7.69921875" customWidth="1"/>
-    <col min="15" max="15" width="39.69921875" customWidth="1"/>
+    <col min="4" max="4" width="10.375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.75" customWidth="1"/>
+    <col min="6" max="6" width="23.25" customWidth="1"/>
+    <col min="7" max="7" width="42.625" customWidth="1"/>
+    <col min="8" max="8" width="5.875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="34.75" customWidth="1"/>
+    <col min="10" max="14" width="7.75" customWidth="1"/>
+    <col min="15" max="15" width="39.75" customWidth="1"/>
+    <col min="16" max="18" width="11" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:19" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-    </row>
-    <row r="2" spans="1:15" ht="19.2" x14ac:dyDescent="0.4">
-      <c r="A2" s="11" t="s">
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+    </row>
+    <row r="2" spans="1:19" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11" t="s">
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="38.4" x14ac:dyDescent="0.4">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
+    <row r="3" spans="1:19" ht="34.5" x14ac:dyDescent="0.3">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
       <c r="J3" s="6" t="s">
         <v>13</v>
       </c>
@@ -2048,19 +2094,31 @@
       <c r="N3" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="O3" s="11"/>
-    </row>
-    <row r="4" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="O3" s="10"/>
+      <c r="P3" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>363</v>
+      </c>
+      <c r="R3" t="s">
+        <v>364</v>
+      </c>
+      <c r="S3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>1</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="12" t="s">
         <v>44</v>
       </c>
       <c r="E4" s="5" t="s">
@@ -2096,14 +2154,23 @@
       <c r="O4" s="5" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P4" s="13">
+        <v>46196</v>
+      </c>
+      <c r="R4" s="13">
+        <v>46196</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>2</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
       <c r="E5" s="5" t="s">
         <v>46</v>
       </c>
@@ -2135,14 +2202,23 @@
       <c r="O5" s="5" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P5" s="13">
+        <v>46196</v>
+      </c>
+      <c r="R5" s="13">
+        <v>46196</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>3</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
       <c r="E6" s="5" t="s">
         <v>48</v>
       </c>
@@ -2172,18 +2248,27 @@
       <c r="O6" s="5" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P6" s="13">
+        <v>46196</v>
+      </c>
+      <c r="R6" s="13">
+        <v>46196</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>4</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="12" t="s">
         <v>51</v>
       </c>
       <c r="E7" s="5" t="s">
@@ -2219,14 +2304,23 @@
       <c r="O7" s="5" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P7" s="13">
+        <v>46196</v>
+      </c>
+      <c r="R7" s="13">
+        <v>46196</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>5</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
       <c r="E8" s="5" t="s">
         <v>53</v>
       </c>
@@ -2260,16 +2354,25 @@
       <c r="O8" s="5" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P8" s="13">
+        <v>46196</v>
+      </c>
+      <c r="R8" s="13">
+        <v>46196</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>6</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
       <c r="E9" s="5" t="s">
         <v>56</v>
       </c>
@@ -2297,18 +2400,27 @@
       <c r="O9" s="5" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P9" s="13">
+        <v>46196</v>
+      </c>
+      <c r="R9" s="13">
+        <v>46196</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>7</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="12" t="s">
         <v>29</v>
       </c>
       <c r="E10" s="5" t="s">
@@ -2342,14 +2454,23 @@
       <c r="O10" s="5" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P10" s="13">
+        <v>46195</v>
+      </c>
+      <c r="R10" s="13">
+        <v>46195</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>8</v>
       </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
       <c r="E11" s="5" t="s">
         <v>65</v>
       </c>
@@ -2381,18 +2502,27 @@
       <c r="O11" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P11" s="13">
+        <v>46195</v>
+      </c>
+      <c r="R11" s="13">
+        <v>46195</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>9</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="12" t="s">
         <v>202</v>
       </c>
       <c r="E12" s="5" t="s">
@@ -2428,14 +2558,23 @@
       <c r="O12" s="5" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P12" s="13">
+        <v>46196</v>
+      </c>
+      <c r="R12" s="13">
+        <v>46196</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>10</v>
       </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
       <c r="E13" s="5" t="s">
         <v>73</v>
       </c>
@@ -2469,14 +2608,23 @@
       <c r="O13" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P13" s="13">
+        <v>46196</v>
+      </c>
+      <c r="R13" s="13">
+        <v>46196</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>11</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
       <c r="E14" s="5" t="s">
         <v>74</v>
       </c>
@@ -2506,18 +2654,27 @@
       <c r="O14" s="5" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P14" s="13">
+        <v>46196</v>
+      </c>
+      <c r="R14" s="13">
+        <v>46196</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>12</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="12" t="s">
         <v>320</v>
       </c>
       <c r="E15" s="5" t="s">
@@ -2553,14 +2710,23 @@
       <c r="O15" s="5" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P15" s="13">
+        <v>46196</v>
+      </c>
+      <c r="R15" s="13">
+        <v>46196</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>13</v>
       </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
       <c r="E16" s="5" t="s">
         <v>83</v>
       </c>
@@ -2590,14 +2756,23 @@
       <c r="O16" s="5" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P16" s="13">
+        <v>46196</v>
+      </c>
+      <c r="R16" s="13">
+        <v>46196</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>14</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
       <c r="E17" s="5" t="s">
         <v>86</v>
       </c>
@@ -2627,18 +2802,27 @@
       <c r="O17" s="5" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P17" s="13">
+        <v>46196</v>
+      </c>
+      <c r="R17" s="13">
+        <v>46196</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>15</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="12" t="s">
         <v>283</v>
       </c>
       <c r="E18" s="5" t="s">
@@ -2674,14 +2858,20 @@
       <c r="O18" s="5" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P18" s="13">
+        <v>46197</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>16</v>
       </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
       <c r="E19" s="5" t="s">
         <v>93</v>
       </c>
@@ -2713,18 +2903,24 @@
       <c r="O19" s="5" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P19" s="13">
+        <v>46197</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>17</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="12" t="s">
         <v>289</v>
       </c>
       <c r="E20" s="5" t="s">
@@ -2760,14 +2956,20 @@
       <c r="O20" s="5" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P20" s="13">
+        <v>46197</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>18</v>
       </c>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
       <c r="E21" s="5" t="s">
         <v>99</v>
       </c>
@@ -2801,14 +3003,20 @@
       <c r="O21" s="5" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P21" s="13">
+        <v>46197</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>19</v>
       </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
       <c r="E22" s="5" t="s">
         <v>100</v>
       </c>
@@ -2840,18 +3048,24 @@
       <c r="O22" s="5" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P22" s="13">
+        <v>46197</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>20</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="12" t="s">
         <v>220</v>
       </c>
       <c r="E23" s="5" t="s">
@@ -2885,14 +3099,20 @@
       <c r="O23" s="5" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P23" s="13">
+        <v>46198</v>
+      </c>
+      <c r="S23" s="14" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>21</v>
       </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
       <c r="E24" s="5" t="s">
         <v>104</v>
       </c>
@@ -2926,14 +3146,18 @@
       <c r="O24" s="5" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P24" s="13">
+        <v>46198</v>
+      </c>
+      <c r="S24" s="15"/>
+    </row>
+    <row r="25" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>22</v>
       </c>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
       <c r="E25" s="5" t="s">
         <v>240</v>
       </c>
@@ -2967,18 +3191,22 @@
       <c r="O25" s="5" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P25" s="13">
+        <v>46198</v>
+      </c>
+      <c r="S25" s="15"/>
+    </row>
+    <row r="26" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>23</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="12" t="s">
         <v>246</v>
       </c>
       <c r="E26" s="5" t="s">
@@ -3014,14 +3242,18 @@
       <c r="O26" s="5" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P26" s="13">
+        <v>46198</v>
+      </c>
+      <c r="S26" s="15"/>
+    </row>
+    <row r="27" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>24</v>
       </c>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
       <c r="E27" s="5" t="s">
         <v>251</v>
       </c>
@@ -3053,18 +3285,22 @@
       <c r="O27" s="5" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P27" s="13">
+        <v>46198</v>
+      </c>
+      <c r="S27" s="15"/>
+    </row>
+    <row r="28" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>25</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="12" t="s">
         <v>107</v>
       </c>
       <c r="E28" s="5" t="s">
@@ -3100,14 +3336,23 @@
       <c r="O28" s="5" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P28" s="13">
+        <v>46195</v>
+      </c>
+      <c r="R28" s="13">
+        <v>46195</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>26</v>
       </c>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
       <c r="E29" s="5" t="s">
         <v>111</v>
       </c>
@@ -3141,14 +3386,23 @@
       <c r="O29" s="5" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P29" s="13">
+        <v>46195</v>
+      </c>
+      <c r="R29" s="13">
+        <v>46195</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>27</v>
       </c>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
       <c r="E30" s="5" t="s">
         <v>115</v>
       </c>
@@ -3178,14 +3432,23 @@
       <c r="O30" s="5" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="31" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P30" s="13">
+        <v>46195</v>
+      </c>
+      <c r="R30" s="13">
+        <v>46195</v>
+      </c>
+      <c r="S30" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>28</v>
       </c>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
       <c r="E31" s="5" t="s">
         <v>256</v>
       </c>
@@ -3213,18 +3476,27 @@
       <c r="O31" s="5" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P31" s="13">
+        <v>46195</v>
+      </c>
+      <c r="R31" s="13">
+        <v>46195</v>
+      </c>
+      <c r="S31" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>29</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D32" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E32" s="5" t="s">
@@ -3256,14 +3528,23 @@
       <c r="O32" s="5" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="33" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P32" s="13">
+        <v>46195</v>
+      </c>
+      <c r="R32" s="13">
+        <v>46195</v>
+      </c>
+      <c r="S32" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>30</v>
       </c>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
       <c r="E33" s="5" t="s">
         <v>126</v>
       </c>
@@ -3293,18 +3574,27 @@
       <c r="O33" s="5" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="34" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P33" s="13">
+        <v>46195</v>
+      </c>
+      <c r="R33" s="13">
+        <v>46195</v>
+      </c>
+      <c r="S33" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>31</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="D34" s="12" t="s">
         <v>319</v>
       </c>
       <c r="E34" s="5" t="s">
@@ -3336,14 +3626,23 @@
       <c r="O34" s="5" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="35" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P34" s="13">
+        <v>46195</v>
+      </c>
+      <c r="R34" s="13">
+        <v>46195</v>
+      </c>
+      <c r="S34" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>32</v>
       </c>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
       <c r="E35" s="5" t="s">
         <v>137</v>
       </c>
@@ -3354,11 +3653,11 @@
         <v>139</v>
       </c>
       <c r="H35" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="I35" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="I35" s="5" t="s">
-        <v>358</v>
-      </c>
       <c r="J35" s="3" t="s">
         <v>45</v>
       </c>
@@ -3375,14 +3674,23 @@
         <v>45</v>
       </c>
       <c r="O35" s="5"/>
-    </row>
-    <row r="36" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P35" s="13">
+        <v>46195</v>
+      </c>
+      <c r="R35" s="13">
+        <v>46195</v>
+      </c>
+      <c r="S35" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>33</v>
       </c>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
       <c r="E36" s="5" t="s">
         <v>140</v>
       </c>
@@ -3412,18 +3720,27 @@
       <c r="O36" s="5" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="37" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P36" s="13">
+        <v>46195</v>
+      </c>
+      <c r="R36" s="13">
+        <v>46195</v>
+      </c>
+      <c r="S36" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>34</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C37" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="D37" s="12" t="s">
         <v>316</v>
       </c>
       <c r="E37" s="5" t="s">
@@ -3459,14 +3776,20 @@
       <c r="O37" s="5" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="38" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P37" s="13">
+        <v>46196</v>
+      </c>
+      <c r="S37" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>35</v>
       </c>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
       <c r="E38" s="5" t="s">
         <v>150</v>
       </c>
@@ -3496,8 +3819,14 @@
       <c r="O38" s="5" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="39" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P38" s="13">
+        <v>46196</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>36</v>
       </c>
@@ -3543,18 +3872,24 @@
       <c r="O39" s="5" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="40" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P39" s="13">
+        <v>46196</v>
+      </c>
+      <c r="S39" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>37</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D40" s="8" t="s">
+      <c r="D40" s="12" t="s">
         <v>318</v>
       </c>
       <c r="E40" s="5" t="s">
@@ -3586,14 +3921,20 @@
       <c r="O40" s="5" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="41" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P40" s="13">
+        <v>46196</v>
+      </c>
+      <c r="S40" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>38</v>
       </c>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
+      <c r="B41" s="12"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
       <c r="E41" s="5" t="s">
         <v>163</v>
       </c>
@@ -3623,14 +3964,20 @@
       <c r="O41" s="5" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="42" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P41" s="13">
+        <v>46196</v>
+      </c>
+      <c r="S41" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>39</v>
       </c>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
+      <c r="B42" s="12"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
       <c r="E42" s="5" t="s">
         <v>167</v>
       </c>
@@ -3660,18 +4007,24 @@
       <c r="O42" s="5" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="43" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P42" s="13">
+        <v>46196</v>
+      </c>
+      <c r="S42" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>40</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C43" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="D43" s="8" t="s">
+      <c r="D43" s="12" t="s">
         <v>317</v>
       </c>
       <c r="E43" s="5" t="s">
@@ -3707,14 +4060,20 @@
       <c r="O43" s="5" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="44" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P43" s="13">
+        <v>46196</v>
+      </c>
+      <c r="S43" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>41</v>
       </c>
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
       <c r="E44" s="5" t="s">
         <v>174</v>
       </c>
@@ -3744,14 +4103,20 @@
       <c r="O44" s="5" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="45" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P44" s="13">
+        <v>46196</v>
+      </c>
+      <c r="S44" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>42</v>
       </c>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
+      <c r="B45" s="12"/>
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
       <c r="E45" s="5" t="s">
         <v>271</v>
       </c>
@@ -3785,18 +4150,24 @@
       <c r="O45" s="5" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="46" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P45" s="13">
+        <v>46196</v>
+      </c>
+      <c r="S45" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>43</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C46" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="D46" s="8" t="s">
+      <c r="D46" s="12" t="s">
         <v>42</v>
       </c>
       <c r="E46" s="5" t="s">
@@ -3832,14 +4203,20 @@
       <c r="O46" s="5" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="47" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P46" s="13">
+        <v>46196</v>
+      </c>
+      <c r="S46" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>44</v>
       </c>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
+      <c r="B47" s="12"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="12"/>
       <c r="E47" s="5" t="s">
         <v>181</v>
       </c>
@@ -3869,18 +4246,24 @@
       <c r="O47" s="5" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="48" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P47" s="13">
+        <v>46196</v>
+      </c>
+      <c r="S47" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>45</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="C48" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="D48" s="8" t="s">
+      <c r="D48" s="12" t="s">
         <v>186</v>
       </c>
       <c r="E48" s="5" t="s">
@@ -3912,14 +4295,23 @@
       <c r="O48" s="5" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="49" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P48" s="13">
+        <v>46196</v>
+      </c>
+      <c r="R48" s="13">
+        <v>46196</v>
+      </c>
+      <c r="S48" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>46</v>
       </c>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
+      <c r="B49" s="12"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="12"/>
       <c r="E49" s="5" t="s">
         <v>191</v>
       </c>
@@ -3947,35 +4339,42 @@
         <v>45</v>
       </c>
       <c r="O49" s="5"/>
+      <c r="P49" s="13">
+        <v>46196</v>
+      </c>
+      <c r="R49" s="13">
+        <v>46196</v>
+      </c>
+      <c r="S49" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="1048576" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P1048576" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="63">
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="J2:N2"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="B43:B45"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="D23:D25"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="D34:D36"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="D28:D31"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="D43:D45"/>
+    <mergeCell ref="D40:D42"/>
     <mergeCell ref="B46:B47"/>
     <mergeCell ref="B48:B49"/>
     <mergeCell ref="C4:C6"/>
@@ -3992,27 +4391,32 @@
     <mergeCell ref="C34:C36"/>
     <mergeCell ref="C37:C38"/>
     <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="D43:D45"/>
-    <mergeCell ref="D40:D42"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="D34:D36"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="D28:D31"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="D23:D25"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="B43:B45"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="J2:N2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4023,14 +4427,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AE8A8BC-1D54-4E00-B190-4FAD897FAAE8}">
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="15.69921875" customWidth="1"/>
-    <col min="3" max="3" width="50.8984375" customWidth="1"/>
-    <col min="4" max="4" width="24.3984375" customWidth="1"/>
+    <col min="1" max="2" width="15.75" customWidth="1"/>
+    <col min="3" max="3" width="50.875" customWidth="1"/>
+    <col min="4" max="4" width="24.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>19</v>
       </c>
@@ -4041,7 +4445,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>22</v>
       </c>
@@ -4052,7 +4456,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>24</v>
       </c>
@@ -4063,7 +4467,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>26</v>
       </c>
@@ -4074,7 +4478,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>28</v>
       </c>
@@ -4085,7 +4489,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>30</v>
       </c>
@@ -4096,7 +4500,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>31</v>
       </c>
@@ -4107,7 +4511,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>32</v>
       </c>
@@ -4118,7 +4522,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>33</v>
       </c>
@@ -4129,7 +4533,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>35</v>
       </c>
@@ -4140,7 +4544,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>37</v>
       </c>
@@ -4148,10 +4552,10 @@
         <v>132</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>38</v>
       </c>
@@ -4162,7 +4566,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>41</v>
       </c>
@@ -4173,7 +4577,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>19</v>
       </c>
@@ -4187,7 +4591,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>3</v>
       </c>
@@ -4201,7 +4605,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>7</v>
       </c>
@@ -4215,7 +4619,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>275</v>
       </c>

--- a/docs/requirements/requirements.xlsx
+++ b/docs/requirements/requirements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Desktop\13-pjt\docs\requirements\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\프로젝트\13-pjt\docs\requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8C58C4-ABCE-40C3-889D-371873B8A82E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9197448-4692-4AEE-990D-C5A6DBEDEEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="3030" windowWidth="31950" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="29505" windowHeight="19230" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="기능요약" sheetId="1" r:id="rId1"/>
@@ -18,11 +18,6 @@
     <sheet name="코드정의" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -1970,7 +1965,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1985,12 +1980,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF16345C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -2008,7 +1997,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2018,52 +2007,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2072,37 +2058,37 @@
     <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2284,25 +2270,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="10" t="s">
         <v>6</v>
       </c>
     </row>
@@ -2885,3634 +2871,3634 @@
     <col min="2" max="3" width="15" style="2" customWidth="1"/>
     <col min="4" max="4" width="16" style="2" customWidth="1"/>
     <col min="5" max="5" width="14" style="2" customWidth="1"/>
-    <col min="6" max="6" width="28.125" style="16" customWidth="1"/>
+    <col min="6" max="6" width="28.125" style="15" customWidth="1"/>
     <col min="7" max="7" width="61.5" customWidth="1"/>
     <col min="8" max="8" width="10" style="2" customWidth="1"/>
     <col min="9" max="9" width="34.75" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="9" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="36" hidden="1" customWidth="1"/>
-    <col min="16" max="18" width="13" style="19" customWidth="1"/>
-    <col min="19" max="19" width="12" style="19" customWidth="1"/>
+    <col min="16" max="18" width="13" style="18" customWidth="1"/>
+    <col min="19" max="19" width="12" style="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
     </row>
     <row r="2" spans="1:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="E2" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="F2" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="29" t="s">
+      <c r="G2" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="29" t="s">
+      <c r="H2" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="29" t="s">
+      <c r="I2" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="29" t="s">
+      <c r="J2" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29" t="s">
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="29" t="s">
+      <c r="P2" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" s="29" t="s">
+      <c r="Q2" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="R2" s="29" t="s">
+      <c r="R2" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="29" t="s">
+      <c r="S2" s="20" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="29"/>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="12" t="s">
+      <c r="A3" s="20"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="L3" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="M3" s="12" t="s">
+      <c r="M3" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="N3" s="12" t="s">
+      <c r="N3" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="O3" s="29"/>
-      <c r="P3" s="29"/>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="29"/>
-      <c r="S3" s="29"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20"/>
+      <c r="R3" s="20"/>
+      <c r="S3" s="20"/>
     </row>
     <row r="4" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15">
+      <c r="A4" s="14">
         <v>1</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="J4" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M4" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N4" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O4" s="9" t="s">
+      <c r="J4" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O4" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="P4" s="17">
+      <c r="P4" s="16">
         <v>46194</v>
       </c>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17" t="s">
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="S4" s="13" t="s">
+      <c r="S4" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15">
+      <c r="A5" s="14">
         <v>2</v>
       </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="13" t="s">
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="J5" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M5" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O5" s="9" t="s">
+      <c r="J5" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O5" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="P5" s="17" t="s">
+      <c r="P5" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="17" t="s">
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="S5" s="13" t="s">
+      <c r="S5" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="15">
+      <c r="A6" s="14">
         <v>3</v>
       </c>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="13" t="s">
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="H6" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="J6" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M6" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N6" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O6" s="9" t="s">
+      <c r="J6" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O6" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="P6" s="17">
+      <c r="P6" s="16">
         <v>46196</v>
       </c>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="17">
+      <c r="Q6" s="16"/>
+      <c r="R6" s="16">
         <v>46196</v>
       </c>
-      <c r="S6" s="13" t="s">
+      <c r="S6" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="15">
+      <c r="A7" s="14">
         <v>4</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="23" t="s">
         <v>124</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="H7" s="13" t="s">
+      <c r="H7" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="J7" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O7" s="9" t="s">
+      <c r="J7" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O7" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="P7" s="17" t="s">
+      <c r="P7" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="Q7" s="17"/>
-      <c r="R7" s="17" t="s">
+      <c r="Q7" s="16"/>
+      <c r="R7" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="S7" s="13" t="s">
+      <c r="S7" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="15">
+      <c r="A8" s="14">
         <v>5</v>
       </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="13" t="s">
+      <c r="B8" s="23"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="H8" s="13" t="s">
+      <c r="H8" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="J8" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M8" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N8" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O8" s="9" t="s">
+      <c r="J8" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O8" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="P8" s="17">
+      <c r="P8" s="16">
         <v>46196</v>
       </c>
-      <c r="Q8" s="17"/>
-      <c r="R8" s="17">
+      <c r="Q8" s="16"/>
+      <c r="R8" s="16">
         <v>46196</v>
       </c>
-      <c r="S8" s="13" t="s">
+      <c r="S8" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="15">
+      <c r="A9" s="14">
         <v>6</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="13" t="s">
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="H9" s="13" t="s">
+      <c r="H9" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I9" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="J9" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N9" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O9" s="9" t="s">
+      <c r="J9" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O9" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="P9" s="17">
+      <c r="P9" s="16">
         <v>46196</v>
       </c>
-      <c r="Q9" s="17"/>
-      <c r="R9" s="17">
+      <c r="Q9" s="16"/>
+      <c r="R9" s="16">
         <v>46196</v>
       </c>
-      <c r="S9" s="13" t="s">
+      <c r="S9" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="15">
+      <c r="A10" s="14">
         <v>7</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="23" t="s">
         <v>580</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="23" t="s">
         <v>582</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="D10" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="H10" s="13" t="s">
+      <c r="H10" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="I10" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="J10" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K10" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M10" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N10" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O10" s="9" t="s">
+      <c r="J10" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O10" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="P10" s="17" t="s">
+      <c r="P10" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="Q10" s="17"/>
-      <c r="R10" s="17" t="s">
+      <c r="Q10" s="16"/>
+      <c r="R10" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="S10" s="13" t="s">
+      <c r="S10" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="15">
+      <c r="A11" s="14">
         <v>8</v>
       </c>
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="23" t="s">
         <v>147</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C11" s="23" t="s">
         <v>148</v>
       </c>
-      <c r="D11" s="26" t="s">
+      <c r="D11" s="23" t="s">
         <v>149</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="H11" s="13" t="s">
+      <c r="H11" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="I11" s="9" t="s">
+      <c r="I11" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="J11" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M11" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N11" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O11" s="9" t="s">
+      <c r="J11" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O11" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="P11" s="17">
+      <c r="P11" s="16">
         <v>46196</v>
       </c>
-      <c r="Q11" s="17"/>
-      <c r="R11" s="17" t="s">
+      <c r="Q11" s="16"/>
+      <c r="R11" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="S11" s="13" t="s">
+      <c r="S11" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="15">
+      <c r="A12" s="14">
         <v>9</v>
       </c>
-      <c r="B12" s="26" t="s">
+      <c r="B12" s="23" t="s">
         <v>581</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="23" t="s">
         <v>583</v>
       </c>
-      <c r="D12" s="26" t="s">
+      <c r="D12" s="23" t="s">
         <v>584</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E12" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="H12" s="13" t="s">
+      <c r="H12" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="J12" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M12" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N12" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O12" s="9" t="s">
+      <c r="J12" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O12" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="P12" s="17">
+      <c r="P12" s="16">
         <v>46196</v>
       </c>
-      <c r="Q12" s="17"/>
-      <c r="R12" s="17" t="s">
+      <c r="Q12" s="16"/>
+      <c r="R12" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="S12" s="13" t="s">
+      <c r="S12" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="15">
+      <c r="A13" s="14">
         <v>10</v>
       </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="13" t="s">
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="H13" s="13" t="s">
+      <c r="H13" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="I13" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="J13" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M13" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N13" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O13" s="9" t="s">
+      <c r="J13" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O13" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="P13" s="17">
+      <c r="P13" s="16">
         <v>46196</v>
       </c>
-      <c r="Q13" s="17"/>
-      <c r="R13" s="17" t="s">
+      <c r="Q13" s="16"/>
+      <c r="R13" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="S13" s="13" t="s">
+      <c r="S13" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="15">
+      <c r="A14" s="14">
         <v>11</v>
       </c>
-      <c r="B14" s="26" t="s">
+      <c r="B14" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="D14" s="26" t="s">
+      <c r="D14" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="H14" s="13" t="s">
+      <c r="H14" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="I14" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="J14" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M14" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N14" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O14" s="9" t="s">
+      <c r="J14" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O14" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="P14" s="17">
+      <c r="P14" s="16">
         <v>46196</v>
       </c>
-      <c r="Q14" s="17"/>
-      <c r="R14" s="17">
+      <c r="Q14" s="16"/>
+      <c r="R14" s="16">
         <v>46196</v>
       </c>
-      <c r="S14" s="13" t="s">
+      <c r="S14" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="15" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="15">
+      <c r="A15" s="14">
         <v>12</v>
       </c>
-      <c r="B15" s="26" t="s">
+      <c r="B15" s="23" t="s">
         <v>585</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="23" t="s">
         <v>586</v>
       </c>
-      <c r="D15" s="26" t="s">
+      <c r="D15" s="23" t="s">
         <v>587</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="H15" s="13" t="s">
+      <c r="H15" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I15" s="9" t="s">
+      <c r="I15" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="J15" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K15" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M15" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N15" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O15" s="9" t="s">
+      <c r="J15" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O15" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="P15" s="17">
+      <c r="P15" s="16">
         <v>46196</v>
       </c>
-      <c r="Q15" s="17"/>
-      <c r="R15" s="17">
+      <c r="Q15" s="16"/>
+      <c r="R15" s="16">
         <v>46196</v>
       </c>
-      <c r="S15" s="13" t="s">
+      <c r="S15" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="15">
+      <c r="A16" s="14">
         <v>13</v>
       </c>
-      <c r="B16" s="26"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="13" t="s">
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="G16" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="H16" s="13" t="s">
+      <c r="H16" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="I16" s="9" t="s">
+      <c r="I16" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="J16" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M16" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N16" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O16" s="9" t="s">
+      <c r="J16" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O16" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="P16" s="17">
+      <c r="P16" s="16">
         <v>46196</v>
       </c>
-      <c r="Q16" s="17"/>
-      <c r="R16" s="17">
+      <c r="Q16" s="16"/>
+      <c r="R16" s="16">
         <v>46196</v>
       </c>
-      <c r="S16" s="13" t="s">
+      <c r="S16" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="15">
+      <c r="A17" s="14">
         <v>14</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="23" t="s">
         <v>181</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="23" t="s">
         <v>182</v>
       </c>
-      <c r="D17" s="26" t="s">
+      <c r="D17" s="23" t="s">
         <v>183</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F17" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="G17" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="H17" s="13" t="s">
+      <c r="H17" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I17" s="9" t="s">
+      <c r="I17" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="J17" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M17" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N17" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O17" s="9" t="s">
+      <c r="J17" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O17" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="P17" s="17" t="s">
+      <c r="P17" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="Q17" s="17"/>
-      <c r="R17" s="17" t="s">
+      <c r="Q17" s="16"/>
+      <c r="R17" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="S17" s="13" t="s">
+      <c r="S17" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="15">
+      <c r="A18" s="14">
         <v>15</v>
       </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="13" t="s">
+      <c r="B18" s="23"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="F18" s="14" t="s">
+      <c r="F18" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="G18" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="H18" s="13" t="s">
+      <c r="H18" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I18" s="9" t="s">
+      <c r="I18" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="J18" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K18" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M18" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N18" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O18" s="9" t="s">
+      <c r="J18" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O18" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="P18" s="17" t="s">
+      <c r="P18" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="Q18" s="17"/>
-      <c r="R18" s="17" t="s">
+      <c r="Q18" s="16"/>
+      <c r="R18" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="S18" s="13" t="s">
+      <c r="S18" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="19" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="15">
+      <c r="A19" s="14">
         <v>16</v>
       </c>
-      <c r="B19" s="26"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="13" t="s">
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="F19" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="H19" s="13" t="s">
+      <c r="H19" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I19" s="9" t="s">
+      <c r="I19" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="J19" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K19" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M19" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N19" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O19" s="9" t="s">
+      <c r="J19" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O19" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="P19" s="17">
+      <c r="P19" s="16">
         <v>46196</v>
       </c>
-      <c r="Q19" s="17"/>
-      <c r="R19" s="17">
+      <c r="Q19" s="16"/>
+      <c r="R19" s="16">
         <v>46196</v>
       </c>
-      <c r="S19" s="13" t="s">
+      <c r="S19" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="20" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="15">
+      <c r="A20" s="14">
         <v>17</v>
       </c>
-      <c r="B20" s="26"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="13" t="s">
+      <c r="B20" s="23"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="F20" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="G20" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="H20" s="13" t="s">
+      <c r="H20" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="I20" s="9" t="s">
+      <c r="I20" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="J20" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K20" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L20" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M20" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N20" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O20" s="9" t="s">
+      <c r="J20" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O20" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="P20" s="17" t="s">
+      <c r="P20" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="Q20" s="17"/>
-      <c r="R20" s="17" t="s">
+      <c r="Q20" s="16"/>
+      <c r="R20" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="S20" s="13" t="s">
+      <c r="S20" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="15">
+      <c r="A21" s="14">
         <v>18</v>
       </c>
-      <c r="B21" s="26"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="13" t="s">
+      <c r="B21" s="23"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="F21" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="H21" s="13" t="s">
+      <c r="H21" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I21" s="9" t="s">
+      <c r="I21" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="J21" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K21" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L21" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M21" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N21" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O21" s="9" t="s">
+      <c r="J21" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N21" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O21" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="P21" s="17">
+      <c r="P21" s="16">
         <v>46195</v>
       </c>
-      <c r="Q21" s="17"/>
-      <c r="R21" s="17">
+      <c r="Q21" s="16"/>
+      <c r="R21" s="16">
         <v>46195</v>
       </c>
-      <c r="S21" s="13" t="s">
+      <c r="S21" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="22" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="15">
+      <c r="A22" s="14">
         <v>19</v>
       </c>
-      <c r="B22" s="26" t="s">
+      <c r="B22" s="23" t="s">
         <v>209</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="C22" s="23" t="s">
         <v>589</v>
       </c>
-      <c r="D22" s="26" t="s">
+      <c r="D22" s="23" t="s">
         <v>588</v>
       </c>
-      <c r="E22" s="13" t="s">
+      <c r="E22" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="F22" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="G22" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="H22" s="13" t="s">
+      <c r="H22" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I22" s="9" t="s">
+      <c r="I22" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="J22" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K22" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L22" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M22" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N22" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O22" s="9" t="s">
+      <c r="J22" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N22" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O22" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="P22" s="17">
+      <c r="P22" s="16">
         <v>46194</v>
       </c>
-      <c r="Q22" s="17"/>
-      <c r="R22" s="17">
+      <c r="Q22" s="16"/>
+      <c r="R22" s="16">
         <v>46194</v>
       </c>
-      <c r="S22" s="13" t="s">
+      <c r="S22" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="15">
+      <c r="A23" s="14">
         <v>20</v>
       </c>
-      <c r="B23" s="26"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="13" t="s">
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="F23" s="14" t="s">
+      <c r="F23" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G23" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="H23" s="13" t="s">
+      <c r="H23" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="I23" s="9" t="s">
+      <c r="I23" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="J23" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K23" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M23" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N23" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O23" s="9" t="s">
+      <c r="J23" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O23" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="P23" s="17">
+      <c r="P23" s="16">
         <v>46196</v>
       </c>
-      <c r="Q23" s="17"/>
-      <c r="R23" s="17">
+      <c r="Q23" s="16"/>
+      <c r="R23" s="16">
         <v>46196</v>
       </c>
-      <c r="S23" s="13" t="s">
+      <c r="S23" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="15">
+      <c r="A24" s="14">
         <v>21</v>
       </c>
-      <c r="B24" s="26"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="13" t="s">
+      <c r="B24" s="23"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="F24" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="G24" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="H24" s="13" t="s">
+      <c r="H24" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="I24" s="9" t="s">
+      <c r="I24" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="J24" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K24" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L24" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M24" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N24" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O24" s="9" t="s">
+      <c r="J24" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O24" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="P24" s="17">
+      <c r="P24" s="16">
         <v>46197</v>
       </c>
-      <c r="Q24" s="17"/>
-      <c r="R24" s="17" t="s">
+      <c r="Q24" s="16"/>
+      <c r="R24" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="S24" s="13" t="s">
+      <c r="S24" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="15">
+      <c r="A25" s="14">
         <v>22</v>
       </c>
-      <c r="B25" s="26" t="s">
+      <c r="B25" s="23" t="s">
         <v>225</v>
       </c>
-      <c r="C25" s="26" t="s">
+      <c r="C25" s="23" t="s">
         <v>590</v>
       </c>
-      <c r="D25" s="26" t="s">
+      <c r="D25" s="23" t="s">
         <v>591</v>
       </c>
-      <c r="E25" s="13" t="s">
+      <c r="E25" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="F25" s="14" t="s">
+      <c r="F25" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="G25" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="H25" s="13" t="s">
+      <c r="H25" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I25" s="9" t="s">
+      <c r="I25" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="J25" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K25" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L25" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M25" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N25" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O25" s="9" t="s">
+      <c r="J25" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N25" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O25" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="P25" s="17">
+      <c r="P25" s="16">
         <v>46194</v>
       </c>
-      <c r="Q25" s="17"/>
-      <c r="R25" s="17">
+      <c r="Q25" s="16"/>
+      <c r="R25" s="16">
         <v>46194</v>
       </c>
-      <c r="S25" s="13" t="s">
+      <c r="S25" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="26" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="15">
+      <c r="A26" s="14">
         <v>23</v>
       </c>
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="13" t="s">
+      <c r="B26" s="23"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="F26" s="14" t="s">
+      <c r="F26" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="G26" s="9" t="s">
+      <c r="G26" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="H26" s="13" t="s">
+      <c r="H26" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="I26" s="9" t="s">
+      <c r="I26" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="J26" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K26" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M26" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N26" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O26" s="9" t="s">
+      <c r="J26" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N26" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O26" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="P26" s="17">
+      <c r="P26" s="16">
         <v>46196</v>
       </c>
-      <c r="Q26" s="17"/>
-      <c r="R26" s="17">
+      <c r="Q26" s="16"/>
+      <c r="R26" s="16">
         <v>46196</v>
       </c>
-      <c r="S26" s="13" t="s">
+      <c r="S26" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="27" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="15">
+      <c r="A27" s="14">
         <v>24</v>
       </c>
-      <c r="B27" s="26"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="13" t="s">
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="F27" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="G27" s="9" t="s">
+      <c r="G27" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="H27" s="13" t="s">
+      <c r="H27" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I27" s="9" t="s">
+      <c r="I27" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="J27" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K27" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L27" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M27" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N27" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O27" s="9" t="s">
+      <c r="J27" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N27" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O27" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="P27" s="17" t="s">
+      <c r="P27" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="Q27" s="17"/>
-      <c r="R27" s="17" t="s">
+      <c r="Q27" s="16"/>
+      <c r="R27" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="S27" s="13" t="s">
+      <c r="S27" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="28" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="15">
+      <c r="A28" s="14">
         <v>25</v>
       </c>
-      <c r="B28" s="26"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="13" t="s">
+      <c r="B28" s="23"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="F28" s="14" t="s">
+      <c r="F28" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="G28" s="9" t="s">
+      <c r="G28" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="H28" s="13" t="s">
+      <c r="H28" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I28" s="9" t="s">
+      <c r="I28" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="J28" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K28" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L28" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M28" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N28" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O28" s="9" t="s">
+      <c r="J28" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N28" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O28" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="P28" s="17">
+      <c r="P28" s="16">
         <v>46195</v>
       </c>
-      <c r="Q28" s="17"/>
-      <c r="R28" s="17">
+      <c r="Q28" s="16"/>
+      <c r="R28" s="16">
         <v>46195</v>
       </c>
-      <c r="S28" s="13" t="s">
+      <c r="S28" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="29" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="15">
+      <c r="A29" s="14">
         <v>26</v>
       </c>
-      <c r="B29" s="26" t="s">
+      <c r="B29" s="23" t="s">
         <v>246</v>
       </c>
-      <c r="C29" s="26" t="s">
+      <c r="C29" s="23" t="s">
         <v>247</v>
       </c>
-      <c r="D29" s="26" t="s">
+      <c r="D29" s="23" t="s">
         <v>592</v>
       </c>
-      <c r="E29" s="13" t="s">
+      <c r="E29" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="F29" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="G29" s="9" t="s">
+      <c r="G29" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="H29" s="13" t="s">
+      <c r="H29" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I29" s="9" t="s">
+      <c r="I29" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="J29" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K29" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L29" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M29" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N29" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O29" s="9" t="s">
+      <c r="J29" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M29" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N29" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O29" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="P29" s="17" t="s">
+      <c r="P29" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="Q29" s="17"/>
-      <c r="R29" s="17" t="s">
+      <c r="Q29" s="16"/>
+      <c r="R29" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="S29" s="13" t="s">
+      <c r="S29" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="30" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="15">
+      <c r="A30" s="14">
         <v>27</v>
       </c>
-      <c r="B30" s="26"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="13" t="s">
+      <c r="B30" s="23"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="F30" s="14" t="s">
+      <c r="F30" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="G30" s="9" t="s">
+      <c r="G30" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="H30" s="13" t="s">
+      <c r="H30" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="I30" s="9" t="s">
+      <c r="I30" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="J30" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K30" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L30" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M30" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N30" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O30" s="9" t="s">
+      <c r="J30" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L30" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M30" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N30" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O30" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="P30" s="17">
+      <c r="P30" s="16">
         <v>46196</v>
       </c>
-      <c r="Q30" s="17"/>
-      <c r="R30" s="17">
+      <c r="Q30" s="16"/>
+      <c r="R30" s="16">
         <v>46196</v>
       </c>
-      <c r="S30" s="13" t="s">
+      <c r="S30" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="31" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="15">
+      <c r="A31" s="14">
         <v>28</v>
       </c>
-      <c r="B31" s="26" t="s">
+      <c r="B31" s="23" t="s">
         <v>258</v>
       </c>
-      <c r="C31" s="26" t="s">
+      <c r="C31" s="23" t="s">
         <v>594</v>
       </c>
-      <c r="D31" s="26" t="s">
+      <c r="D31" s="23" t="s">
         <v>593</v>
       </c>
-      <c r="E31" s="13" t="s">
+      <c r="E31" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="F31" s="14" t="s">
+      <c r="F31" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="G31" s="9" t="s">
+      <c r="G31" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="H31" s="13" t="s">
+      <c r="H31" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I31" s="9" t="s">
+      <c r="I31" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="J31" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K31" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L31" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M31" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N31" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O31" s="9" t="s">
+      <c r="J31" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L31" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M31" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N31" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O31" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="P31" s="17">
+      <c r="P31" s="16">
         <v>46195</v>
       </c>
-      <c r="Q31" s="17"/>
-      <c r="R31" s="17">
+      <c r="Q31" s="16"/>
+      <c r="R31" s="16">
         <v>46195</v>
       </c>
-      <c r="S31" s="13" t="s">
+      <c r="S31" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="32" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="15">
+      <c r="A32" s="14">
         <v>29</v>
       </c>
-      <c r="B32" s="26"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="13" t="s">
+      <c r="B32" s="23"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="12" t="s">
         <v>264</v>
       </c>
-      <c r="F32" s="14" t="s">
+      <c r="F32" s="13" t="s">
         <v>265</v>
       </c>
-      <c r="G32" s="9" t="s">
+      <c r="G32" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="H32" s="13" t="s">
+      <c r="H32" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I32" s="9" t="s">
+      <c r="I32" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="J32" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K32" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L32" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M32" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N32" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O32" s="9" t="s">
+      <c r="J32" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L32" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M32" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N32" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O32" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="P32" s="17">
+      <c r="P32" s="16">
         <v>46195</v>
       </c>
-      <c r="Q32" s="17"/>
-      <c r="R32" s="17">
+      <c r="Q32" s="16"/>
+      <c r="R32" s="16">
         <v>46195</v>
       </c>
-      <c r="S32" s="13" t="s">
+      <c r="S32" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="33" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="15">
+      <c r="A33" s="14">
         <v>30</v>
       </c>
-      <c r="B33" s="26" t="s">
+      <c r="B33" s="23" t="s">
         <v>269</v>
       </c>
-      <c r="C33" s="26" t="s">
+      <c r="C33" s="23" t="s">
         <v>595</v>
       </c>
-      <c r="D33" s="26" t="s">
+      <c r="D33" s="23" t="s">
         <v>596</v>
       </c>
-      <c r="E33" s="13" t="s">
+      <c r="E33" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="F33" s="14" t="s">
+      <c r="F33" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="G33" s="9" t="s">
+      <c r="G33" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="H33" s="13" t="s">
+      <c r="H33" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I33" s="9" t="s">
+      <c r="I33" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="J33" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K33" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L33" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M33" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N33" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O33" s="9" t="s">
+      <c r="J33" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L33" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M33" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N33" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O33" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="P33" s="17">
+      <c r="P33" s="16">
         <v>46196</v>
       </c>
-      <c r="Q33" s="17"/>
-      <c r="R33" s="17">
+      <c r="Q33" s="16"/>
+      <c r="R33" s="16">
         <v>46196</v>
       </c>
-      <c r="S33" s="13" t="s">
+      <c r="S33" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="34" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="15">
+      <c r="A34" s="14">
         <v>31</v>
       </c>
-      <c r="B34" s="26"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="13" t="s">
+      <c r="B34" s="23"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="F34" s="14" t="s">
+      <c r="F34" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="G34" s="9" t="s">
+      <c r="G34" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="H34" s="13" t="s">
+      <c r="H34" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I34" s="9" t="s">
+      <c r="I34" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="J34" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K34" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L34" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M34" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N34" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O34" s="9" t="s">
+      <c r="J34" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L34" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M34" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N34" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O34" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="P34" s="17">
+      <c r="P34" s="16">
         <v>46196</v>
       </c>
-      <c r="Q34" s="17"/>
-      <c r="R34" s="17">
+      <c r="Q34" s="16"/>
+      <c r="R34" s="16">
         <v>46196</v>
       </c>
-      <c r="S34" s="13" t="s">
+      <c r="S34" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="35" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="15">
+      <c r="A35" s="14">
         <v>32</v>
       </c>
-      <c r="B35" s="26" t="s">
+      <c r="B35" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C35" s="26" t="s">
+      <c r="C35" s="23" t="s">
         <v>280</v>
       </c>
-      <c r="D35" s="26" t="s">
+      <c r="D35" s="23" t="s">
         <v>281</v>
       </c>
-      <c r="E35" s="13" t="s">
+      <c r="E35" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="F35" s="14" t="s">
+      <c r="F35" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="G35" s="9" t="s">
+      <c r="G35" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="H35" s="13" t="s">
+      <c r="H35" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I35" s="9" t="s">
+      <c r="I35" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="J35" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K35" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L35" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M35" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N35" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O35" s="9" t="s">
+      <c r="J35" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L35" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M35" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N35" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O35" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="P35" s="17">
+      <c r="P35" s="16">
         <v>46196</v>
       </c>
-      <c r="Q35" s="17"/>
-      <c r="R35" s="17">
+      <c r="Q35" s="16"/>
+      <c r="R35" s="16">
         <v>46196</v>
       </c>
-      <c r="S35" s="13" t="s">
+      <c r="S35" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="36" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="15">
+      <c r="A36" s="14">
         <v>33</v>
       </c>
-      <c r="B36" s="26"/>
-      <c r="C36" s="26"/>
-      <c r="D36" s="26"/>
-      <c r="E36" s="13" t="s">
+      <c r="B36" s="23"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="F36" s="22" t="s">
+      <c r="F36" s="26" t="s">
         <v>288</v>
       </c>
-      <c r="G36" s="23" t="s">
+      <c r="G36" s="27" t="s">
         <v>605</v>
       </c>
-      <c r="H36" s="21" t="s">
+      <c r="H36" s="28" t="s">
         <v>133</v>
       </c>
-      <c r="I36" s="23" t="s">
+      <c r="I36" s="27" t="s">
         <v>289</v>
       </c>
-      <c r="J36" s="24" t="s">
-        <v>110</v>
-      </c>
-      <c r="K36" s="24" t="s">
-        <v>110</v>
-      </c>
-      <c r="L36" s="24" t="s">
-        <v>110</v>
-      </c>
-      <c r="M36" s="24" t="s">
-        <v>110</v>
-      </c>
-      <c r="N36" s="24" t="s">
-        <v>110</v>
-      </c>
-      <c r="O36" s="23" t="s">
+      <c r="J36" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="K36" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="L36" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="M36" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="N36" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="O36" s="27" t="s">
         <v>290</v>
       </c>
-      <c r="P36" s="25" t="s">
+      <c r="P36" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="Q36" s="25"/>
-      <c r="R36" s="25" t="s">
+      <c r="Q36" s="30"/>
+      <c r="R36" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="S36" s="21" t="s">
+      <c r="S36" s="28" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="37" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="15">
+      <c r="A37" s="14">
         <v>34</v>
       </c>
-      <c r="B37" s="26"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="13" t="s">
+      <c r="B37" s="23"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="12" t="s">
         <v>291</v>
       </c>
-      <c r="F37" s="14" t="s">
+      <c r="F37" s="13" t="s">
         <v>292</v>
       </c>
-      <c r="G37" s="9" t="s">
+      <c r="G37" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="H37" s="13" t="s">
+      <c r="H37" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I37" s="9" t="s">
+      <c r="I37" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="J37" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K37" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L37" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M37" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N37" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O37" s="9" t="s">
+      <c r="J37" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L37" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M37" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N37" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O37" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="P37" s="17">
+      <c r="P37" s="16">
         <v>46196</v>
       </c>
-      <c r="Q37" s="17"/>
-      <c r="R37" s="17">
+      <c r="Q37" s="16"/>
+      <c r="R37" s="16">
         <v>46196</v>
       </c>
-      <c r="S37" s="13" t="s">
+      <c r="S37" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="38" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="15">
+      <c r="A38" s="14">
         <v>35</v>
       </c>
-      <c r="B38" s="26"/>
-      <c r="C38" s="26"/>
-      <c r="D38" s="26"/>
-      <c r="E38" s="13" t="s">
+      <c r="B38" s="23"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="F38" s="14" t="s">
+      <c r="F38" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="G38" s="9" t="s">
+      <c r="G38" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="H38" s="13" t="s">
+      <c r="H38" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I38" s="9" t="s">
+      <c r="I38" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="J38" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K38" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L38" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M38" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N38" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O38" s="9" t="s">
+      <c r="J38" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L38" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M38" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N38" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O38" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="P38" s="17">
+      <c r="P38" s="16">
         <v>46196</v>
       </c>
-      <c r="Q38" s="17"/>
-      <c r="R38" s="17">
+      <c r="Q38" s="16"/>
+      <c r="R38" s="16">
         <v>46196</v>
       </c>
-      <c r="S38" s="13" t="s">
+      <c r="S38" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="39" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="15">
+      <c r="A39" s="14">
         <v>36</v>
       </c>
-      <c r="B39" s="26"/>
-      <c r="C39" s="26"/>
-      <c r="D39" s="26"/>
-      <c r="E39" s="13" t="s">
+      <c r="B39" s="23"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="12" t="s">
         <v>301</v>
       </c>
-      <c r="F39" s="14" t="s">
+      <c r="F39" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="G39" s="9" t="s">
+      <c r="G39" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="H39" s="13" t="s">
+      <c r="H39" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="I39" s="9" t="s">
+      <c r="I39" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="J39" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K39" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L39" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M39" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N39" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O39" s="9" t="s">
+      <c r="J39" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L39" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M39" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N39" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O39" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="P39" s="17" t="s">
+      <c r="P39" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="Q39" s="17"/>
-      <c r="R39" s="17" t="s">
+      <c r="Q39" s="16"/>
+      <c r="R39" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="S39" s="13" t="s">
+      <c r="S39" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="40" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="15">
+      <c r="A40" s="14">
         <v>37</v>
       </c>
-      <c r="B40" s="26"/>
-      <c r="C40" s="26"/>
-      <c r="D40" s="26"/>
-      <c r="E40" s="13" t="s">
+      <c r="B40" s="23"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="12" t="s">
         <v>306</v>
       </c>
-      <c r="F40" s="14" t="s">
+      <c r="F40" s="13" t="s">
         <v>307</v>
       </c>
-      <c r="G40" s="9" t="s">
+      <c r="G40" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="H40" s="13" t="s">
+      <c r="H40" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="I40" s="9" t="s">
+      <c r="I40" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="J40" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K40" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L40" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M40" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N40" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O40" s="9" t="s">
+      <c r="J40" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L40" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M40" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N40" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O40" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="P40" s="17" t="s">
+      <c r="P40" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="Q40" s="17"/>
-      <c r="R40" s="17" t="s">
+      <c r="Q40" s="16"/>
+      <c r="R40" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="S40" s="13" t="s">
+      <c r="S40" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="41" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="15">
+      <c r="A41" s="14">
         <v>38</v>
       </c>
-      <c r="B41" s="26"/>
-      <c r="C41" s="26"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="13" t="s">
+      <c r="B41" s="23"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="12" t="s">
         <v>311</v>
       </c>
-      <c r="F41" s="14" t="s">
+      <c r="F41" s="13" t="s">
         <v>312</v>
       </c>
-      <c r="G41" s="9" t="s">
+      <c r="G41" s="8" t="s">
         <v>313</v>
       </c>
-      <c r="H41" s="13" t="s">
+      <c r="H41" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I41" s="9" t="s">
+      <c r="I41" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="J41" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K41" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L41" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M41" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N41" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O41" s="9" t="s">
+      <c r="J41" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L41" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M41" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N41" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O41" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="P41" s="17">
+      <c r="P41" s="16">
         <v>46196</v>
       </c>
-      <c r="Q41" s="17"/>
-      <c r="R41" s="17">
+      <c r="Q41" s="16"/>
+      <c r="R41" s="16">
         <v>46196</v>
       </c>
-      <c r="S41" s="13" t="s">
+      <c r="S41" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="42" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="15">
+      <c r="A42" s="14">
         <v>39</v>
       </c>
-      <c r="B42" s="26"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="26"/>
-      <c r="E42" s="13" t="s">
+      <c r="B42" s="23"/>
+      <c r="C42" s="23"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="12" t="s">
         <v>316</v>
       </c>
-      <c r="F42" s="14" t="s">
+      <c r="F42" s="13" t="s">
         <v>317</v>
       </c>
-      <c r="G42" s="9" t="s">
+      <c r="G42" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="H42" s="13" t="s">
+      <c r="H42" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="I42" s="9" t="s">
+      <c r="I42" s="8" t="s">
         <v>319</v>
       </c>
-      <c r="J42" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K42" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L42" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M42" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N42" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O42" s="9" t="s">
+      <c r="J42" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L42" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M42" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N42" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O42" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="P42" s="17" t="s">
+      <c r="P42" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="Q42" s="17"/>
-      <c r="R42" s="17" t="s">
+      <c r="Q42" s="16"/>
+      <c r="R42" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="S42" s="13" t="s">
+      <c r="S42" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="15">
+      <c r="A43" s="14">
         <v>40</v>
       </c>
-      <c r="B43" s="26"/>
-      <c r="C43" s="26"/>
-      <c r="D43" s="26"/>
-      <c r="E43" s="13" t="s">
+      <c r="B43" s="23"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="12" t="s">
         <v>321</v>
       </c>
-      <c r="F43" s="14" t="s">
+      <c r="F43" s="13" t="s">
         <v>607</v>
       </c>
-      <c r="G43" s="9" t="s">
+      <c r="G43" s="8" t="s">
         <v>606</v>
       </c>
-      <c r="H43" s="13" t="s">
+      <c r="H43" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I43" s="9" t="s">
+      <c r="I43" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="J43" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K43" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L43" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M43" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N43" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O43" s="9" t="s">
+      <c r="J43" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K43" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L43" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M43" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N43" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O43" s="8" t="s">
         <v>323</v>
       </c>
-      <c r="P43" s="17" t="s">
+      <c r="P43" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="Q43" s="17"/>
-      <c r="R43" s="17" t="s">
+      <c r="Q43" s="16"/>
+      <c r="R43" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="S43" s="13" t="s">
+      <c r="S43" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="44" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="15">
+      <c r="A44" s="14">
         <v>41</v>
       </c>
-      <c r="B44" s="26"/>
-      <c r="C44" s="26"/>
-      <c r="D44" s="26"/>
-      <c r="E44" s="13" t="s">
+      <c r="B44" s="23"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="23"/>
+      <c r="E44" s="12" t="s">
         <v>324</v>
       </c>
-      <c r="F44" s="14" t="s">
+      <c r="F44" s="13" t="s">
         <v>325</v>
       </c>
-      <c r="G44" s="9" t="s">
+      <c r="G44" s="8" t="s">
         <v>326</v>
       </c>
-      <c r="H44" s="13" t="s">
+      <c r="H44" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="I44" s="9" t="s">
+      <c r="I44" s="8" t="s">
         <v>327</v>
       </c>
-      <c r="J44" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K44" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L44" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M44" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N44" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O44" s="9" t="s">
+      <c r="J44" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L44" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M44" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N44" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O44" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="P44" s="17" t="s">
+      <c r="P44" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="Q44" s="17"/>
-      <c r="R44" s="17" t="s">
+      <c r="Q44" s="16"/>
+      <c r="R44" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="S44" s="13" t="s">
+      <c r="S44" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="45" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="15">
+      <c r="A45" s="14">
         <v>42</v>
       </c>
-      <c r="B45" s="26" t="s">
+      <c r="B45" s="23" t="s">
         <v>329</v>
       </c>
-      <c r="C45" s="26" t="s">
+      <c r="C45" s="23" t="s">
         <v>330</v>
       </c>
-      <c r="D45" s="26" t="s">
+      <c r="D45" s="23" t="s">
         <v>331</v>
       </c>
-      <c r="E45" s="13" t="s">
+      <c r="E45" s="12" t="s">
         <v>332</v>
       </c>
-      <c r="F45" s="14" t="s">
+      <c r="F45" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="G45" s="9" t="s">
+      <c r="G45" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="H45" s="13" t="s">
+      <c r="H45" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I45" s="9" t="s">
+      <c r="I45" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="J45" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K45" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L45" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M45" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N45" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O45" s="9" t="s">
+      <c r="J45" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K45" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L45" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M45" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N45" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O45" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="P45" s="17" t="s">
+      <c r="P45" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="Q45" s="17"/>
-      <c r="R45" s="17" t="s">
+      <c r="Q45" s="16"/>
+      <c r="R45" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="S45" s="13" t="s">
+      <c r="S45" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="46" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="15">
+      <c r="A46" s="14">
         <v>43</v>
       </c>
-      <c r="B46" s="26"/>
-      <c r="C46" s="26"/>
-      <c r="D46" s="26"/>
-      <c r="E46" s="13" t="s">
+      <c r="B46" s="23"/>
+      <c r="C46" s="23"/>
+      <c r="D46" s="23"/>
+      <c r="E46" s="12" t="s">
         <v>337</v>
       </c>
-      <c r="F46" s="14" t="s">
+      <c r="F46" s="13" t="s">
         <v>338</v>
       </c>
-      <c r="G46" s="9" t="s">
+      <c r="G46" s="8" t="s">
         <v>604</v>
       </c>
-      <c r="H46" s="13" t="s">
+      <c r="H46" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I46" s="9" t="s">
+      <c r="I46" s="8" t="s">
         <v>339</v>
       </c>
-      <c r="J46" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K46" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L46" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M46" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N46" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O46" s="9" t="s">
+      <c r="J46" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K46" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L46" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M46" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N46" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O46" s="8" t="s">
         <v>340</v>
       </c>
-      <c r="P46" s="17" t="s">
+      <c r="P46" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="Q46" s="17"/>
-      <c r="R46" s="17" t="s">
+      <c r="Q46" s="16"/>
+      <c r="R46" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="S46" s="13" t="s">
+      <c r="S46" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="47" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="15">
+      <c r="A47" s="14">
         <v>44</v>
       </c>
-      <c r="B47" s="26"/>
-      <c r="C47" s="26"/>
-      <c r="D47" s="26"/>
-      <c r="E47" s="13" t="s">
+      <c r="B47" s="23"/>
+      <c r="C47" s="23"/>
+      <c r="D47" s="23"/>
+      <c r="E47" s="12" t="s">
         <v>341</v>
       </c>
-      <c r="F47" s="14" t="s">
+      <c r="F47" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="G47" s="9" t="s">
+      <c r="G47" s="8" t="s">
         <v>343</v>
       </c>
-      <c r="H47" s="13" t="s">
+      <c r="H47" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I47" s="9" t="s">
+      <c r="I47" s="8" t="s">
         <v>344</v>
       </c>
-      <c r="J47" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K47" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L47" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M47" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N47" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O47" s="9" t="s">
+      <c r="J47" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L47" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M47" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N47" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O47" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="P47" s="17" t="s">
+      <c r="P47" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="Q47" s="17"/>
-      <c r="R47" s="17" t="s">
+      <c r="Q47" s="16"/>
+      <c r="R47" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="S47" s="13" t="s">
+      <c r="S47" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="48" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="15">
+      <c r="A48" s="14">
         <v>46</v>
       </c>
-      <c r="B48" s="26"/>
-      <c r="C48" s="26"/>
-      <c r="D48" s="26"/>
-      <c r="E48" s="13" t="s">
+      <c r="B48" s="23"/>
+      <c r="C48" s="23"/>
+      <c r="D48" s="23"/>
+      <c r="E48" s="12" t="s">
         <v>608</v>
       </c>
-      <c r="F48" s="14" t="s">
+      <c r="F48" s="13" t="s">
         <v>346</v>
       </c>
-      <c r="G48" s="9" t="s">
+      <c r="G48" s="8" t="s">
         <v>347</v>
       </c>
-      <c r="H48" s="13" t="s">
+      <c r="H48" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="I48" s="9" t="s">
+      <c r="I48" s="8" t="s">
         <v>348</v>
       </c>
-      <c r="J48" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K48" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L48" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M48" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N48" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O48" s="9" t="s">
+      <c r="J48" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K48" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L48" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M48" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N48" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O48" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="P48" s="17">
+      <c r="P48" s="16">
         <v>46195</v>
       </c>
-      <c r="Q48" s="17"/>
-      <c r="R48" s="17">
+      <c r="Q48" s="16"/>
+      <c r="R48" s="16">
         <v>46195</v>
       </c>
-      <c r="S48" s="13" t="s">
+      <c r="S48" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="49" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="15">
+      <c r="A49" s="14">
         <v>47</v>
       </c>
-      <c r="B49" s="26" t="s">
+      <c r="B49" s="23" t="s">
         <v>350</v>
       </c>
-      <c r="C49" s="26" t="s">
+      <c r="C49" s="23" t="s">
         <v>351</v>
       </c>
-      <c r="D49" s="26" t="s">
+      <c r="D49" s="23" t="s">
         <v>352</v>
       </c>
-      <c r="E49" s="13" t="s">
+      <c r="E49" s="12" t="s">
         <v>353</v>
       </c>
-      <c r="F49" s="14" t="s">
+      <c r="F49" s="13" t="s">
         <v>354</v>
       </c>
-      <c r="G49" s="9" t="s">
+      <c r="G49" s="8" t="s">
         <v>355</v>
       </c>
-      <c r="H49" s="13" t="s">
+      <c r="H49" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I49" s="9" t="s">
+      <c r="I49" s="8" t="s">
         <v>356</v>
       </c>
-      <c r="J49" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K49" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L49" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M49" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N49" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O49" s="9" t="s">
+      <c r="J49" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K49" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L49" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M49" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N49" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O49" s="8" t="s">
         <v>357</v>
       </c>
-      <c r="P49" s="17">
+      <c r="P49" s="16">
         <v>46195</v>
       </c>
-      <c r="Q49" s="17"/>
-      <c r="R49" s="17">
+      <c r="Q49" s="16"/>
+      <c r="R49" s="16">
         <v>46195</v>
       </c>
-      <c r="S49" s="13" t="s">
+      <c r="S49" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="50" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="15">
+      <c r="A50" s="14">
         <v>48</v>
       </c>
-      <c r="B50" s="26"/>
-      <c r="C50" s="26"/>
-      <c r="D50" s="26"/>
-      <c r="E50" s="13" t="s">
+      <c r="B50" s="23"/>
+      <c r="C50" s="23"/>
+      <c r="D50" s="23"/>
+      <c r="E50" s="12" t="s">
         <v>358</v>
       </c>
-      <c r="F50" s="14" t="s">
+      <c r="F50" s="13" t="s">
         <v>359</v>
       </c>
-      <c r="G50" s="9" t="s">
+      <c r="G50" s="8" t="s">
         <v>360</v>
       </c>
-      <c r="H50" s="13" t="s">
+      <c r="H50" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I50" s="9" t="s">
+      <c r="I50" s="8" t="s">
         <v>361</v>
       </c>
-      <c r="J50" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K50" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L50" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M50" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N50" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O50" s="9" t="s">
+      <c r="J50" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K50" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L50" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M50" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N50" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O50" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="P50" s="17">
+      <c r="P50" s="16">
         <v>46195</v>
       </c>
-      <c r="Q50" s="17"/>
-      <c r="R50" s="17">
+      <c r="Q50" s="16"/>
+      <c r="R50" s="16">
         <v>46195</v>
       </c>
-      <c r="S50" s="13" t="s">
+      <c r="S50" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="51" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="15">
+      <c r="A51" s="14">
         <v>49</v>
       </c>
-      <c r="B51" s="26"/>
-      <c r="C51" s="26"/>
-      <c r="D51" s="26"/>
-      <c r="E51" s="13" t="s">
+      <c r="B51" s="23"/>
+      <c r="C51" s="23"/>
+      <c r="D51" s="23"/>
+      <c r="E51" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="F51" s="14" t="s">
+      <c r="F51" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="G51" s="9" t="s">
+      <c r="G51" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="H51" s="13" t="s">
+      <c r="H51" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="I51" s="9" t="s">
+      <c r="I51" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="J51" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K51" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L51" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M51" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N51" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O51" s="9" t="s">
+      <c r="J51" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L51" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M51" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N51" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O51" s="8" t="s">
         <v>367</v>
       </c>
-      <c r="P51" s="17">
+      <c r="P51" s="16">
         <v>46195</v>
       </c>
-      <c r="Q51" s="17"/>
-      <c r="R51" s="17">
+      <c r="Q51" s="16"/>
+      <c r="R51" s="16">
         <v>46195</v>
       </c>
-      <c r="S51" s="13" t="s">
+      <c r="S51" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="52" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="15">
+      <c r="A52" s="14">
         <v>50</v>
       </c>
-      <c r="B52" s="26"/>
-      <c r="C52" s="26"/>
-      <c r="D52" s="26"/>
-      <c r="E52" s="13" t="s">
+      <c r="B52" s="23"/>
+      <c r="C52" s="23"/>
+      <c r="D52" s="23"/>
+      <c r="E52" s="12" t="s">
         <v>368</v>
       </c>
-      <c r="F52" s="14" t="s">
+      <c r="F52" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="G52" s="9" t="s">
+      <c r="G52" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="H52" s="13" t="s">
+      <c r="H52" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I52" s="9" t="s">
+      <c r="I52" s="8" t="s">
         <v>371</v>
       </c>
-      <c r="J52" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K52" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L52" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M52" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N52" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O52" s="9" t="s">
+      <c r="J52" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K52" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L52" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M52" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N52" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O52" s="8" t="s">
         <v>372</v>
       </c>
-      <c r="P52" s="17">
+      <c r="P52" s="16">
         <v>46195</v>
       </c>
-      <c r="Q52" s="17"/>
-      <c r="R52" s="17">
+      <c r="Q52" s="16"/>
+      <c r="R52" s="16">
         <v>46195</v>
       </c>
-      <c r="S52" s="13" t="s">
+      <c r="S52" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="53" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="15">
+      <c r="A53" s="14">
         <v>51</v>
       </c>
-      <c r="B53" s="26" t="s">
+      <c r="B53" s="23" t="s">
         <v>373</v>
       </c>
-      <c r="C53" s="26" t="s">
+      <c r="C53" s="23" t="s">
         <v>374</v>
       </c>
-      <c r="D53" s="26" t="s">
+      <c r="D53" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="E53" s="13" t="s">
+      <c r="E53" s="12" t="s">
         <v>375</v>
       </c>
-      <c r="F53" s="14" t="s">
+      <c r="F53" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="G53" s="9" t="s">
+      <c r="G53" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="H53" s="13" t="s">
+      <c r="H53" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I53" s="9" t="s">
+      <c r="I53" s="8" t="s">
         <v>378</v>
       </c>
-      <c r="J53" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K53" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L53" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M53" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N53" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O53" s="9" t="s">
+      <c r="J53" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K53" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L53" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M53" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N53" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O53" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="P53" s="17">
+      <c r="P53" s="16">
         <v>46195</v>
       </c>
-      <c r="Q53" s="17"/>
-      <c r="R53" s="17">
+      <c r="Q53" s="16"/>
+      <c r="R53" s="16">
         <v>46195</v>
       </c>
-      <c r="S53" s="13" t="s">
+      <c r="S53" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="54" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="15">
+      <c r="A54" s="14">
         <v>52</v>
       </c>
-      <c r="B54" s="26"/>
-      <c r="C54" s="26"/>
-      <c r="D54" s="26"/>
-      <c r="E54" s="13" t="s">
+      <c r="B54" s="23"/>
+      <c r="C54" s="23"/>
+      <c r="D54" s="23"/>
+      <c r="E54" s="12" t="s">
         <v>380</v>
       </c>
-      <c r="F54" s="14" t="s">
+      <c r="F54" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="G54" s="9" t="s">
+      <c r="G54" s="8" t="s">
         <v>382</v>
       </c>
-      <c r="H54" s="13" t="s">
+      <c r="H54" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="I54" s="9" t="s">
+      <c r="I54" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="J54" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K54" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L54" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M54" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N54" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O54" s="9" t="s">
+      <c r="J54" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K54" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L54" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M54" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N54" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O54" s="8" t="s">
         <v>384</v>
       </c>
-      <c r="P54" s="17">
+      <c r="P54" s="16">
         <v>46195</v>
       </c>
-      <c r="Q54" s="17"/>
-      <c r="R54" s="17">
+      <c r="Q54" s="16"/>
+      <c r="R54" s="16">
         <v>46195</v>
       </c>
-      <c r="S54" s="13" t="s">
+      <c r="S54" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="55" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="15">
+      <c r="A55" s="14">
         <v>53</v>
       </c>
-      <c r="B55" s="26"/>
-      <c r="C55" s="26"/>
-      <c r="D55" s="26"/>
-      <c r="E55" s="13" t="s">
+      <c r="B55" s="23"/>
+      <c r="C55" s="23"/>
+      <c r="D55" s="23"/>
+      <c r="E55" s="12" t="s">
         <v>385</v>
       </c>
-      <c r="F55" s="14" t="s">
+      <c r="F55" s="13" t="s">
         <v>386</v>
       </c>
-      <c r="G55" s="9" t="s">
+      <c r="G55" s="8" t="s">
         <v>387</v>
       </c>
-      <c r="H55" s="13" t="s">
+      <c r="H55" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I55" s="9" t="s">
+      <c r="I55" s="8" t="s">
         <v>388</v>
       </c>
-      <c r="J55" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K55" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L55" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M55" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N55" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O55" s="9" t="s">
+      <c r="J55" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K55" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L55" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M55" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N55" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O55" s="8" t="s">
         <v>389</v>
       </c>
-      <c r="P55" s="17">
+      <c r="P55" s="16">
         <v>46195</v>
       </c>
-      <c r="Q55" s="17"/>
-      <c r="R55" s="17">
+      <c r="Q55" s="16"/>
+      <c r="R55" s="16">
         <v>46195</v>
       </c>
-      <c r="S55" s="13" t="s">
+      <c r="S55" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="56" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="15">
+      <c r="A56" s="14">
         <v>54</v>
       </c>
-      <c r="B56" s="26"/>
-      <c r="C56" s="26"/>
-      <c r="D56" s="26"/>
-      <c r="E56" s="13" t="s">
+      <c r="B56" s="23"/>
+      <c r="C56" s="23"/>
+      <c r="D56" s="23"/>
+      <c r="E56" s="12" t="s">
         <v>390</v>
       </c>
-      <c r="F56" s="14" t="s">
+      <c r="F56" s="13" t="s">
         <v>391</v>
       </c>
-      <c r="G56" s="9" t="s">
+      <c r="G56" s="8" t="s">
         <v>392</v>
       </c>
-      <c r="H56" s="13" t="s">
+      <c r="H56" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I56" s="9" t="s">
+      <c r="I56" s="8" t="s">
         <v>393</v>
       </c>
-      <c r="J56" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K56" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L56" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M56" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N56" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O56" s="9" t="s">
+      <c r="J56" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K56" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L56" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M56" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N56" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O56" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="P56" s="17">
+      <c r="P56" s="16">
         <v>46195</v>
       </c>
-      <c r="Q56" s="17"/>
-      <c r="R56" s="17">
+      <c r="Q56" s="16"/>
+      <c r="R56" s="16">
         <v>46195</v>
       </c>
-      <c r="S56" s="13" t="s">
+      <c r="S56" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="57" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="15">
+      <c r="A57" s="14">
         <v>55</v>
       </c>
-      <c r="B57" s="26"/>
-      <c r="C57" s="26"/>
-      <c r="D57" s="26"/>
-      <c r="E57" s="13" t="s">
+      <c r="B57" s="23"/>
+      <c r="C57" s="23"/>
+      <c r="D57" s="23"/>
+      <c r="E57" s="12" t="s">
         <v>395</v>
       </c>
-      <c r="F57" s="14" t="s">
+      <c r="F57" s="13" t="s">
         <v>396</v>
       </c>
-      <c r="G57" s="9" t="s">
+      <c r="G57" s="8" t="s">
         <v>397</v>
       </c>
-      <c r="H57" s="13" t="s">
+      <c r="H57" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I57" s="9" t="s">
+      <c r="I57" s="8" t="s">
         <v>398</v>
       </c>
-      <c r="J57" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K57" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L57" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M57" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N57" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O57" s="9" t="s">
+      <c r="J57" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K57" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L57" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M57" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N57" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O57" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="P57" s="17">
+      <c r="P57" s="16">
         <v>46195</v>
       </c>
-      <c r="Q57" s="17"/>
-      <c r="R57" s="17">
+      <c r="Q57" s="16"/>
+      <c r="R57" s="16">
         <v>46195</v>
       </c>
-      <c r="S57" s="13" t="s">
+      <c r="S57" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="58" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="15">
+      <c r="A58" s="14">
         <v>56</v>
       </c>
-      <c r="B58" s="26" t="s">
+      <c r="B58" s="23" t="s">
         <v>400</v>
       </c>
-      <c r="C58" s="26" t="s">
+      <c r="C58" s="23" t="s">
         <v>401</v>
       </c>
-      <c r="D58" s="26" t="s">
+      <c r="D58" s="23" t="s">
         <v>402</v>
       </c>
-      <c r="E58" s="13" t="s">
+      <c r="E58" s="12" t="s">
         <v>403</v>
       </c>
-      <c r="F58" s="14" t="s">
+      <c r="F58" s="13" t="s">
         <v>404</v>
       </c>
-      <c r="G58" s="9" t="s">
+      <c r="G58" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="H58" s="13" t="s">
+      <c r="H58" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I58" s="9" t="s">
+      <c r="I58" s="8" t="s">
         <v>406</v>
       </c>
-      <c r="J58" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K58" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L58" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M58" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N58" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O58" s="9" t="s">
+      <c r="J58" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K58" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L58" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M58" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N58" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O58" s="8" t="s">
         <v>407</v>
       </c>
-      <c r="P58" s="17">
+      <c r="P58" s="16">
         <v>46194</v>
       </c>
-      <c r="Q58" s="17"/>
-      <c r="R58" s="17">
+      <c r="Q58" s="16"/>
+      <c r="R58" s="16">
         <v>46194</v>
       </c>
-      <c r="S58" s="13" t="s">
+      <c r="S58" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="59" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="15">
+      <c r="A59" s="14">
         <v>57</v>
       </c>
-      <c r="B59" s="26"/>
-      <c r="C59" s="26"/>
-      <c r="D59" s="26"/>
-      <c r="E59" s="13" t="s">
+      <c r="B59" s="23"/>
+      <c r="C59" s="23"/>
+      <c r="D59" s="23"/>
+      <c r="E59" s="12" t="s">
         <v>408</v>
       </c>
-      <c r="F59" s="14" t="s">
+      <c r="F59" s="13" t="s">
         <v>409</v>
       </c>
-      <c r="G59" s="9" t="s">
+      <c r="G59" s="8" t="s">
         <v>410</v>
       </c>
-      <c r="H59" s="13" t="s">
+      <c r="H59" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="I59" s="9" t="s">
+      <c r="I59" s="8" t="s">
         <v>411</v>
       </c>
-      <c r="J59" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K59" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L59" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M59" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N59" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O59" s="9" t="s">
+      <c r="J59" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K59" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L59" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M59" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N59" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O59" s="8" t="s">
         <v>412</v>
       </c>
-      <c r="P59" s="17">
+      <c r="P59" s="16">
         <v>46196</v>
       </c>
-      <c r="Q59" s="17"/>
-      <c r="R59" s="17">
+      <c r="Q59" s="16"/>
+      <c r="R59" s="16">
         <v>46196</v>
       </c>
-      <c r="S59" s="13" t="s">
+      <c r="S59" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="60" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="15">
+      <c r="A60" s="14">
         <v>58</v>
       </c>
-      <c r="B60" s="26"/>
-      <c r="C60" s="26"/>
-      <c r="D60" s="26"/>
-      <c r="E60" s="13" t="s">
+      <c r="B60" s="23"/>
+      <c r="C60" s="23"/>
+      <c r="D60" s="23"/>
+      <c r="E60" s="12" t="s">
         <v>413</v>
       </c>
-      <c r="F60" s="14" t="s">
+      <c r="F60" s="13" t="s">
         <v>414</v>
       </c>
-      <c r="G60" s="9" t="s">
+      <c r="G60" s="8" t="s">
         <v>415</v>
       </c>
-      <c r="H60" s="13" t="s">
+      <c r="H60" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I60" s="9" t="s">
+      <c r="I60" s="8" t="s">
         <v>416</v>
       </c>
-      <c r="J60" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K60" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L60" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M60" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N60" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O60" s="9" t="s">
+      <c r="J60" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K60" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L60" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M60" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N60" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O60" s="8" t="s">
         <v>417</v>
       </c>
-      <c r="P60" s="17">
+      <c r="P60" s="16">
         <v>46196</v>
       </c>
-      <c r="Q60" s="17"/>
-      <c r="R60" s="17">
+      <c r="Q60" s="16"/>
+      <c r="R60" s="16">
         <v>46196</v>
       </c>
-      <c r="S60" s="13" t="s">
+      <c r="S60" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="61" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="15">
+      <c r="A61" s="14">
         <v>59</v>
       </c>
-      <c r="B61" s="26"/>
-      <c r="C61" s="26"/>
-      <c r="D61" s="26"/>
-      <c r="E61" s="13" t="s">
+      <c r="B61" s="23"/>
+      <c r="C61" s="23"/>
+      <c r="D61" s="23"/>
+      <c r="E61" s="12" t="s">
         <v>418</v>
       </c>
-      <c r="F61" s="14" t="s">
+      <c r="F61" s="13" t="s">
         <v>419</v>
       </c>
-      <c r="G61" s="9" t="s">
+      <c r="G61" s="8" t="s">
         <v>420</v>
       </c>
-      <c r="H61" s="13" t="s">
+      <c r="H61" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="I61" s="9" t="s">
+      <c r="I61" s="8" t="s">
         <v>421</v>
       </c>
-      <c r="J61" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K61" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L61" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M61" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N61" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O61" s="9" t="s">
+      <c r="J61" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K61" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L61" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M61" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N61" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O61" s="8" t="s">
         <v>422</v>
       </c>
-      <c r="P61" s="17">
+      <c r="P61" s="16">
         <v>46196</v>
       </c>
-      <c r="Q61" s="17"/>
-      <c r="R61" s="17">
+      <c r="Q61" s="16"/>
+      <c r="R61" s="16">
         <v>46196</v>
       </c>
-      <c r="S61" s="13" t="s">
+      <c r="S61" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="62" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="15">
+      <c r="A62" s="14">
         <v>60</v>
       </c>
-      <c r="B62" s="26" t="s">
+      <c r="B62" s="23" t="s">
         <v>423</v>
       </c>
-      <c r="C62" s="26" t="s">
+      <c r="C62" s="23" t="s">
         <v>424</v>
       </c>
-      <c r="D62" s="26" t="s">
+      <c r="D62" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="E62" s="13" t="s">
+      <c r="E62" s="12" t="s">
         <v>425</v>
       </c>
-      <c r="F62" s="14" t="s">
+      <c r="F62" s="13" t="s">
         <v>426</v>
       </c>
-      <c r="G62" s="9" t="s">
+      <c r="G62" s="8" t="s">
         <v>427</v>
       </c>
-      <c r="H62" s="13" t="s">
+      <c r="H62" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="I62" s="9" t="s">
+      <c r="I62" s="8" t="s">
         <v>428</v>
       </c>
-      <c r="J62" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K62" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L62" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M62" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N62" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O62" s="9" t="s">
+      <c r="J62" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K62" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L62" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M62" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N62" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O62" s="8" t="s">
         <v>429</v>
       </c>
-      <c r="P62" s="17">
+      <c r="P62" s="16">
         <v>46196</v>
       </c>
-      <c r="Q62" s="17"/>
-      <c r="R62" s="17">
+      <c r="Q62" s="16"/>
+      <c r="R62" s="16">
         <v>46196</v>
       </c>
-      <c r="S62" s="13" t="s">
+      <c r="S62" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="63" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="15">
+      <c r="A63" s="14">
         <v>61</v>
       </c>
-      <c r="B63" s="26"/>
-      <c r="C63" s="26"/>
-      <c r="D63" s="26"/>
-      <c r="E63" s="13" t="s">
+      <c r="B63" s="23"/>
+      <c r="C63" s="23"/>
+      <c r="D63" s="23"/>
+      <c r="E63" s="12" t="s">
         <v>430</v>
       </c>
-      <c r="F63" s="14" t="s">
+      <c r="F63" s="13" t="s">
         <v>431</v>
       </c>
-      <c r="G63" s="9" t="s">
+      <c r="G63" s="8" t="s">
         <v>432</v>
       </c>
-      <c r="H63" s="13" t="s">
+      <c r="H63" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="I63" s="9" t="s">
+      <c r="I63" s="8" t="s">
         <v>433</v>
       </c>
-      <c r="J63" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K63" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L63" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M63" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N63" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O63" s="9" t="s">
+      <c r="J63" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K63" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L63" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M63" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N63" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O63" s="8" t="s">
         <v>434</v>
       </c>
-      <c r="P63" s="17">
+      <c r="P63" s="16">
         <v>46196</v>
       </c>
-      <c r="Q63" s="17" t="s">
+      <c r="Q63" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="R63" s="17" t="s">
+      <c r="R63" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="S63" s="13" t="s">
+      <c r="S63" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="64" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="15">
+      <c r="A64" s="14">
         <v>62</v>
       </c>
-      <c r="B64" s="26"/>
-      <c r="C64" s="26"/>
-      <c r="D64" s="26"/>
-      <c r="E64" s="13" t="s">
+      <c r="B64" s="23"/>
+      <c r="C64" s="23"/>
+      <c r="D64" s="23"/>
+      <c r="E64" s="12" t="s">
         <v>435</v>
       </c>
-      <c r="F64" s="14" t="s">
+      <c r="F64" s="13" t="s">
         <v>436</v>
       </c>
-      <c r="G64" s="9" t="s">
+      <c r="G64" s="8" t="s">
         <v>437</v>
       </c>
-      <c r="H64" s="13" t="s">
+      <c r="H64" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="I64" s="9" t="s">
+      <c r="I64" s="8" t="s">
         <v>438</v>
       </c>
-      <c r="J64" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K64" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L64" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M64" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N64" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O64" s="9" t="s">
+      <c r="J64" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K64" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L64" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M64" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N64" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O64" s="8" t="s">
         <v>439</v>
       </c>
-      <c r="P64" s="17" t="s">
+      <c r="P64" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="Q64" s="17"/>
-      <c r="R64" s="17" t="s">
+      <c r="Q64" s="16"/>
+      <c r="R64" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="S64" s="13" t="s">
+      <c r="S64" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="65" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="15">
+      <c r="A65" s="14">
         <v>63</v>
       </c>
-      <c r="B65" s="26" t="s">
+      <c r="B65" s="23" t="s">
         <v>440</v>
       </c>
-      <c r="C65" s="26" t="s">
+      <c r="C65" s="23" t="s">
         <v>441</v>
       </c>
-      <c r="D65" s="26" t="s">
+      <c r="D65" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="E65" s="13" t="s">
+      <c r="E65" s="12" t="s">
         <v>442</v>
       </c>
-      <c r="F65" s="14" t="s">
+      <c r="F65" s="13" t="s">
         <v>443</v>
       </c>
-      <c r="G65" s="9" t="s">
+      <c r="G65" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="H65" s="13" t="s">
+      <c r="H65" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I65" s="9" t="s">
+      <c r="I65" s="8" t="s">
         <v>445</v>
       </c>
-      <c r="J65" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K65" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L65" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M65" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N65" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O65" s="9" t="s">
+      <c r="J65" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K65" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L65" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M65" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N65" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O65" s="8" t="s">
         <v>446</v>
       </c>
-      <c r="P65" s="17">
+      <c r="P65" s="16">
         <v>46194</v>
       </c>
-      <c r="Q65" s="17"/>
-      <c r="R65" s="17">
+      <c r="Q65" s="16"/>
+      <c r="R65" s="16">
         <v>46194</v>
       </c>
-      <c r="S65" s="13" t="s">
+      <c r="S65" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="66" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="15">
+      <c r="A66" s="14">
         <v>64</v>
       </c>
-      <c r="B66" s="26"/>
-      <c r="C66" s="26"/>
-      <c r="D66" s="26"/>
-      <c r="E66" s="13" t="s">
+      <c r="B66" s="23"/>
+      <c r="C66" s="23"/>
+      <c r="D66" s="23"/>
+      <c r="E66" s="12" t="s">
         <v>447</v>
       </c>
-      <c r="F66" s="14" t="s">
+      <c r="F66" s="13" t="s">
         <v>448</v>
       </c>
-      <c r="G66" s="9" t="s">
+      <c r="G66" s="8" t="s">
         <v>449</v>
       </c>
-      <c r="H66" s="13" t="s">
+      <c r="H66" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="I66" s="9" t="s">
+      <c r="I66" s="8" t="s">
         <v>450</v>
       </c>
-      <c r="J66" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K66" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L66" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M66" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N66" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O66" s="9" t="s">
+      <c r="J66" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K66" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L66" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M66" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N66" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O66" s="8" t="s">
         <v>451</v>
       </c>
-      <c r="P66" s="17">
+      <c r="P66" s="16">
         <v>46194</v>
       </c>
-      <c r="Q66" s="17"/>
-      <c r="R66" s="17">
+      <c r="Q66" s="16"/>
+      <c r="R66" s="16">
         <v>46194</v>
       </c>
-      <c r="S66" s="13" t="s">
+      <c r="S66" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="67" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="15">
+      <c r="A67" s="14">
         <v>65</v>
       </c>
-      <c r="B67" s="26"/>
-      <c r="C67" s="26"/>
-      <c r="D67" s="26"/>
-      <c r="E67" s="13" t="s">
+      <c r="B67" s="23"/>
+      <c r="C67" s="23"/>
+      <c r="D67" s="23"/>
+      <c r="E67" s="12" t="s">
         <v>452</v>
       </c>
-      <c r="F67" s="14" t="s">
+      <c r="F67" s="13" t="s">
         <v>453</v>
       </c>
-      <c r="G67" s="9" t="s">
+      <c r="G67" s="8" t="s">
         <v>454</v>
       </c>
-      <c r="H67" s="13" t="s">
+      <c r="H67" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I67" s="9" t="s">
+      <c r="I67" s="8" t="s">
         <v>455</v>
       </c>
-      <c r="J67" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K67" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L67" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M67" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N67" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O67" s="9" t="s">
+      <c r="J67" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K67" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L67" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M67" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N67" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O67" s="8" t="s">
         <v>456</v>
       </c>
-      <c r="P67" s="17">
+      <c r="P67" s="16">
         <v>46194</v>
       </c>
-      <c r="Q67" s="17"/>
-      <c r="R67" s="17">
+      <c r="Q67" s="16"/>
+      <c r="R67" s="16">
         <v>46194</v>
       </c>
-      <c r="S67" s="13" t="s">
+      <c r="S67" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="68" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="15">
+      <c r="A68" s="14">
         <v>66</v>
       </c>
-      <c r="B68" s="26"/>
-      <c r="C68" s="26"/>
-      <c r="D68" s="26"/>
-      <c r="E68" s="13" t="s">
+      <c r="B68" s="23"/>
+      <c r="C68" s="23"/>
+      <c r="D68" s="23"/>
+      <c r="E68" s="12" t="s">
         <v>457</v>
       </c>
-      <c r="F68" s="14" t="s">
+      <c r="F68" s="13" t="s">
         <v>458</v>
       </c>
-      <c r="G68" s="9" t="s">
+      <c r="G68" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="H68" s="13" t="s">
+      <c r="H68" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="I68" s="9" t="s">
+      <c r="I68" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="J68" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K68" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L68" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M68" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N68" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O68" s="9" t="s">
+      <c r="J68" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K68" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L68" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M68" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N68" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O68" s="8" t="s">
         <v>461</v>
       </c>
-      <c r="P68" s="17">
+      <c r="P68" s="16">
         <v>46194</v>
       </c>
-      <c r="Q68" s="17"/>
-      <c r="R68" s="17">
+      <c r="Q68" s="16"/>
+      <c r="R68" s="16">
         <v>46194</v>
       </c>
-      <c r="S68" s="13" t="s">
+      <c r="S68" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="69" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="15">
+      <c r="A69" s="14">
         <v>67</v>
       </c>
-      <c r="B69" s="26" t="s">
+      <c r="B69" s="23" t="s">
         <v>462</v>
       </c>
-      <c r="C69" s="26" t="s">
+      <c r="C69" s="23" t="s">
         <v>463</v>
       </c>
-      <c r="D69" s="26" t="s">
+      <c r="D69" s="23" t="s">
         <v>464</v>
       </c>
-      <c r="E69" s="13" t="s">
+      <c r="E69" s="12" t="s">
         <v>465</v>
       </c>
-      <c r="F69" s="14" t="s">
+      <c r="F69" s="13" t="s">
         <v>466</v>
       </c>
-      <c r="G69" s="9" t="s">
+      <c r="G69" s="8" t="s">
         <v>467</v>
       </c>
-      <c r="H69" s="13" t="s">
+      <c r="H69" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I69" s="9" t="s">
+      <c r="I69" s="8" t="s">
         <v>468</v>
       </c>
-      <c r="J69" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K69" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L69" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M69" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N69" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="O69" s="9" t="s">
+      <c r="J69" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K69" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L69" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M69" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N69" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O69" s="8" t="s">
         <v>469</v>
       </c>
-      <c r="P69" s="17">
+      <c r="P69" s="16">
         <v>46196</v>
       </c>
-      <c r="Q69" s="17"/>
-      <c r="R69" s="17">
+      <c r="Q69" s="16"/>
+      <c r="R69" s="16">
         <v>46196</v>
       </c>
-      <c r="S69" s="13" t="s">
+      <c r="S69" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="70" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="10">
+      <c r="A70" s="9">
         <v>68</v>
       </c>
-      <c r="B70" s="26"/>
-      <c r="C70" s="26"/>
-      <c r="D70" s="26"/>
-      <c r="E70" s="10" t="s">
+      <c r="B70" s="23"/>
+      <c r="C70" s="23"/>
+      <c r="D70" s="23"/>
+      <c r="E70" s="9" t="s">
         <v>470</v>
       </c>
-      <c r="F70" s="14" t="s">
+      <c r="F70" s="13" t="s">
         <v>471</v>
       </c>
       <c r="G70" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="H70" s="10" t="s">
+      <c r="H70" s="9" t="s">
         <v>108</v>
       </c>
       <c r="I70" s="5" t="s">
@@ -6536,40 +6522,40 @@
       <c r="O70" s="5" t="s">
         <v>474</v>
       </c>
-      <c r="P70" s="17">
+      <c r="P70" s="16">
         <v>46196</v>
       </c>
-      <c r="Q70" s="17"/>
-      <c r="R70" s="17">
+      <c r="Q70" s="16"/>
+      <c r="R70" s="16">
         <v>46196</v>
       </c>
-      <c r="S70" s="13" t="s">
+      <c r="S70" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="71" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="10">
+      <c r="A71" s="9">
         <v>69</v>
       </c>
-      <c r="B71" s="27" t="s">
+      <c r="B71" s="24" t="s">
         <v>475</v>
       </c>
-      <c r="C71" s="28" t="s">
+      <c r="C71" s="25" t="s">
         <v>598</v>
       </c>
-      <c r="D71" s="27" t="s">
+      <c r="D71" s="24" t="s">
         <v>476</v>
       </c>
-      <c r="E71" s="10" t="s">
+      <c r="E71" s="9" t="s">
         <v>477</v>
       </c>
-      <c r="F71" s="14" t="s">
+      <c r="F71" s="13" t="s">
         <v>478</v>
       </c>
       <c r="G71" s="5" t="s">
         <v>479</v>
       </c>
-      <c r="H71" s="10" t="s">
+      <c r="H71" s="9" t="s">
         <v>108</v>
       </c>
       <c r="I71" s="5" t="s">
@@ -6593,34 +6579,34 @@
       <c r="O71" s="5" t="s">
         <v>481</v>
       </c>
-      <c r="P71" s="17">
+      <c r="P71" s="16">
         <v>46196</v>
       </c>
-      <c r="Q71" s="17"/>
-      <c r="R71" s="17">
+      <c r="Q71" s="16"/>
+      <c r="R71" s="16">
         <v>46196</v>
       </c>
-      <c r="S71" s="13" t="s">
+      <c r="S71" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="72" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="10">
+      <c r="A72" s="9">
         <v>70</v>
       </c>
-      <c r="B72" s="27"/>
-      <c r="C72" s="27"/>
-      <c r="D72" s="27"/>
-      <c r="E72" s="10" t="s">
+      <c r="B72" s="24"/>
+      <c r="C72" s="24"/>
+      <c r="D72" s="24"/>
+      <c r="E72" s="9" t="s">
         <v>482</v>
       </c>
-      <c r="F72" s="14" t="s">
+      <c r="F72" s="13" t="s">
         <v>483</v>
       </c>
       <c r="G72" s="5" t="s">
         <v>484</v>
       </c>
-      <c r="H72" s="10" t="s">
+      <c r="H72" s="9" t="s">
         <v>133</v>
       </c>
       <c r="I72" s="5" t="s">
@@ -6644,40 +6630,40 @@
       <c r="O72" s="5" t="s">
         <v>486</v>
       </c>
-      <c r="P72" s="17">
+      <c r="P72" s="16">
         <v>46196</v>
       </c>
-      <c r="Q72" s="17"/>
-      <c r="R72" s="17">
+      <c r="Q72" s="16"/>
+      <c r="R72" s="16">
         <v>46196</v>
       </c>
-      <c r="S72" s="13" t="s">
+      <c r="S72" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="73" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="10">
+      <c r="A73" s="9">
         <v>71</v>
       </c>
-      <c r="B73" s="27" t="s">
+      <c r="B73" s="24" t="s">
         <v>487</v>
       </c>
-      <c r="C73" s="28" t="s">
+      <c r="C73" s="25" t="s">
         <v>599</v>
       </c>
-      <c r="D73" s="28" t="s">
+      <c r="D73" s="25" t="s">
         <v>597</v>
       </c>
-      <c r="E73" s="10" t="s">
+      <c r="E73" s="9" t="s">
         <v>488</v>
       </c>
-      <c r="F73" s="14" t="s">
+      <c r="F73" s="13" t="s">
         <v>489</v>
       </c>
       <c r="G73" s="5" t="s">
         <v>490</v>
       </c>
-      <c r="H73" s="10" t="s">
+      <c r="H73" s="9" t="s">
         <v>108</v>
       </c>
       <c r="I73" s="5" t="s">
@@ -6701,34 +6687,34 @@
       <c r="O73" s="5" t="s">
         <v>492</v>
       </c>
-      <c r="P73" s="17">
+      <c r="P73" s="16">
         <v>46196</v>
       </c>
-      <c r="Q73" s="17"/>
-      <c r="R73" s="17">
+      <c r="Q73" s="16"/>
+      <c r="R73" s="16">
         <v>46196</v>
       </c>
-      <c r="S73" s="13" t="s">
+      <c r="S73" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="74" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="10">
+      <c r="A74" s="9">
         <v>72</v>
       </c>
-      <c r="B74" s="27"/>
-      <c r="C74" s="27"/>
-      <c r="D74" s="27"/>
-      <c r="E74" s="10" t="s">
+      <c r="B74" s="24"/>
+      <c r="C74" s="24"/>
+      <c r="D74" s="24"/>
+      <c r="E74" s="9" t="s">
         <v>493</v>
       </c>
-      <c r="F74" s="14" t="s">
+      <c r="F74" s="13" t="s">
         <v>494</v>
       </c>
       <c r="G74" s="5" t="s">
         <v>495</v>
       </c>
-      <c r="H74" s="10" t="s">
+      <c r="H74" s="9" t="s">
         <v>108</v>
       </c>
       <c r="I74" s="5" t="s">
@@ -6752,34 +6738,34 @@
       <c r="O74" s="5" t="s">
         <v>497</v>
       </c>
-      <c r="P74" s="17">
+      <c r="P74" s="16">
         <v>46196</v>
       </c>
-      <c r="Q74" s="17"/>
-      <c r="R74" s="17">
+      <c r="Q74" s="16"/>
+      <c r="R74" s="16">
         <v>46196</v>
       </c>
-      <c r="S74" s="13" t="s">
+      <c r="S74" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="75" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="10">
+      <c r="A75" s="9">
         <v>73</v>
       </c>
-      <c r="B75" s="27"/>
-      <c r="C75" s="27"/>
-      <c r="D75" s="27"/>
-      <c r="E75" s="10" t="s">
+      <c r="B75" s="24"/>
+      <c r="C75" s="24"/>
+      <c r="D75" s="24"/>
+      <c r="E75" s="9" t="s">
         <v>498</v>
       </c>
-      <c r="F75" s="14" t="s">
+      <c r="F75" s="13" t="s">
         <v>499</v>
       </c>
       <c r="G75" s="5" t="s">
         <v>500</v>
       </c>
-      <c r="H75" s="10" t="s">
+      <c r="H75" s="9" t="s">
         <v>133</v>
       </c>
       <c r="I75" s="5" t="s">
@@ -6803,40 +6789,40 @@
       <c r="O75" s="5" t="s">
         <v>502</v>
       </c>
-      <c r="P75" s="17">
+      <c r="P75" s="16">
         <v>46196</v>
       </c>
-      <c r="Q75" s="17"/>
-      <c r="R75" s="17">
+      <c r="Q75" s="16"/>
+      <c r="R75" s="16">
         <v>46196</v>
       </c>
-      <c r="S75" s="13" t="s">
+      <c r="S75" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="76" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="10">
+      <c r="A76" s="9">
         <v>74</v>
       </c>
-      <c r="B76" s="27" t="s">
+      <c r="B76" s="24" t="s">
         <v>503</v>
       </c>
-      <c r="C76" s="28" t="s">
+      <c r="C76" s="25" t="s">
         <v>600</v>
       </c>
-      <c r="D76" s="28" t="s">
+      <c r="D76" s="25" t="s">
         <v>601</v>
       </c>
-      <c r="E76" s="10" t="s">
+      <c r="E76" s="9" t="s">
         <v>504</v>
       </c>
-      <c r="F76" s="14" t="s">
+      <c r="F76" s="13" t="s">
         <v>505</v>
       </c>
       <c r="G76" s="5" t="s">
         <v>506</v>
       </c>
-      <c r="H76" s="10" t="s">
+      <c r="H76" s="9" t="s">
         <v>108</v>
       </c>
       <c r="I76" s="5" t="s">
@@ -6860,34 +6846,34 @@
       <c r="O76" s="5" t="s">
         <v>508</v>
       </c>
-      <c r="P76" s="17">
+      <c r="P76" s="16">
         <v>46196</v>
       </c>
-      <c r="Q76" s="17"/>
-      <c r="R76" s="17">
+      <c r="Q76" s="16"/>
+      <c r="R76" s="16">
         <v>46196</v>
       </c>
-      <c r="S76" s="13" t="s">
+      <c r="S76" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="77" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="10">
+      <c r="A77" s="9">
         <v>75</v>
       </c>
-      <c r="B77" s="27"/>
-      <c r="C77" s="27"/>
-      <c r="D77" s="27"/>
-      <c r="E77" s="10" t="s">
+      <c r="B77" s="24"/>
+      <c r="C77" s="24"/>
+      <c r="D77" s="24"/>
+      <c r="E77" s="9" t="s">
         <v>509</v>
       </c>
-      <c r="F77" s="14" t="s">
+      <c r="F77" s="13" t="s">
         <v>510</v>
       </c>
       <c r="G77" s="5" t="s">
         <v>511</v>
       </c>
-      <c r="H77" s="10" t="s">
+      <c r="H77" s="9" t="s">
         <v>108</v>
       </c>
       <c r="I77" s="5" t="s">
@@ -6911,34 +6897,34 @@
       <c r="O77" s="5" t="s">
         <v>513</v>
       </c>
-      <c r="P77" s="17">
+      <c r="P77" s="16">
         <v>46196</v>
       </c>
-      <c r="Q77" s="17"/>
-      <c r="R77" s="17">
+      <c r="Q77" s="16"/>
+      <c r="R77" s="16">
         <v>46196</v>
       </c>
-      <c r="S77" s="13" t="s">
+      <c r="S77" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="78" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="10">
+      <c r="A78" s="9">
         <v>76</v>
       </c>
-      <c r="B78" s="27"/>
-      <c r="C78" s="27"/>
-      <c r="D78" s="27"/>
-      <c r="E78" s="10" t="s">
+      <c r="B78" s="24"/>
+      <c r="C78" s="24"/>
+      <c r="D78" s="24"/>
+      <c r="E78" s="9" t="s">
         <v>514</v>
       </c>
-      <c r="F78" s="14" t="s">
+      <c r="F78" s="13" t="s">
         <v>515</v>
       </c>
       <c r="G78" s="5" t="s">
         <v>516</v>
       </c>
-      <c r="H78" s="10" t="s">
+      <c r="H78" s="9" t="s">
         <v>108</v>
       </c>
       <c r="I78" s="5" t="s">
@@ -6962,34 +6948,34 @@
       <c r="O78" s="5" t="s">
         <v>518</v>
       </c>
-      <c r="P78" s="17">
+      <c r="P78" s="16">
         <v>46196</v>
       </c>
-      <c r="Q78" s="17"/>
-      <c r="R78" s="17">
+      <c r="Q78" s="16"/>
+      <c r="R78" s="16">
         <v>46196</v>
       </c>
-      <c r="S78" s="13" t="s">
+      <c r="S78" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="79" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="10">
+      <c r="A79" s="9">
         <v>77</v>
       </c>
-      <c r="B79" s="27"/>
-      <c r="C79" s="27"/>
-      <c r="D79" s="27"/>
-      <c r="E79" s="10" t="s">
+      <c r="B79" s="24"/>
+      <c r="C79" s="24"/>
+      <c r="D79" s="24"/>
+      <c r="E79" s="9" t="s">
         <v>519</v>
       </c>
-      <c r="F79" s="14" t="s">
+      <c r="F79" s="13" t="s">
         <v>520</v>
       </c>
       <c r="G79" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="H79" s="10" t="s">
+      <c r="H79" s="9" t="s">
         <v>133</v>
       </c>
       <c r="I79" s="5" t="s">
@@ -7013,40 +6999,40 @@
       <c r="O79" s="5" t="s">
         <v>523</v>
       </c>
-      <c r="P79" s="17">
+      <c r="P79" s="16">
         <v>46196</v>
       </c>
-      <c r="Q79" s="17"/>
-      <c r="R79" s="17">
+      <c r="Q79" s="16"/>
+      <c r="R79" s="16">
         <v>46196</v>
       </c>
-      <c r="S79" s="13" t="s">
+      <c r="S79" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="80" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="10">
+      <c r="A80" s="9">
         <v>78</v>
       </c>
-      <c r="B80" s="27" t="s">
+      <c r="B80" s="24" t="s">
         <v>524</v>
       </c>
-      <c r="C80" s="27" t="s">
+      <c r="C80" s="24" t="s">
         <v>165</v>
       </c>
-      <c r="D80" s="27" t="s">
+      <c r="D80" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="E80" s="10" t="s">
+      <c r="E80" s="9" t="s">
         <v>525</v>
       </c>
-      <c r="F80" s="14" t="s">
+      <c r="F80" s="13" t="s">
         <v>526</v>
       </c>
       <c r="G80" s="5" t="s">
         <v>527</v>
       </c>
-      <c r="H80" s="10" t="s">
+      <c r="H80" s="9" t="s">
         <v>108</v>
       </c>
       <c r="I80" s="5" t="s">
@@ -7070,36 +7056,36 @@
       <c r="O80" s="5" t="s">
         <v>529</v>
       </c>
-      <c r="P80" s="17">
+      <c r="P80" s="16">
         <v>46196</v>
       </c>
-      <c r="Q80" s="17">
+      <c r="Q80" s="16">
         <v>46197</v>
       </c>
-      <c r="R80" s="17">
+      <c r="R80" s="16">
         <v>46197</v>
       </c>
-      <c r="S80" s="13" t="s">
+      <c r="S80" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="81" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="10">
+      <c r="A81" s="9">
         <v>79</v>
       </c>
-      <c r="B81" s="27"/>
-      <c r="C81" s="27"/>
-      <c r="D81" s="27"/>
-      <c r="E81" s="10" t="s">
+      <c r="B81" s="24"/>
+      <c r="C81" s="24"/>
+      <c r="D81" s="24"/>
+      <c r="E81" s="9" t="s">
         <v>530</v>
       </c>
-      <c r="F81" s="14" t="s">
+      <c r="F81" s="13" t="s">
         <v>531</v>
       </c>
       <c r="G81" s="5" t="s">
         <v>532</v>
       </c>
-      <c r="H81" s="10" t="s">
+      <c r="H81" s="9" t="s">
         <v>108</v>
       </c>
       <c r="I81" s="5" t="s">
@@ -7123,34 +7109,34 @@
       <c r="O81" s="5" t="s">
         <v>534</v>
       </c>
-      <c r="P81" s="17">
+      <c r="P81" s="16">
         <v>46196</v>
       </c>
-      <c r="Q81" s="17"/>
-      <c r="R81" s="17">
+      <c r="Q81" s="16"/>
+      <c r="R81" s="16">
         <v>46196</v>
       </c>
-      <c r="S81" s="13" t="s">
+      <c r="S81" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="82" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="10">
+      <c r="A82" s="9">
         <v>80</v>
       </c>
-      <c r="B82" s="27"/>
-      <c r="C82" s="27"/>
-      <c r="D82" s="27"/>
-      <c r="E82" s="10" t="s">
+      <c r="B82" s="24"/>
+      <c r="C82" s="24"/>
+      <c r="D82" s="24"/>
+      <c r="E82" s="9" t="s">
         <v>535</v>
       </c>
-      <c r="F82" s="14" t="s">
+      <c r="F82" s="13" t="s">
         <v>536</v>
       </c>
       <c r="G82" s="5" t="s">
         <v>537</v>
       </c>
-      <c r="H82" s="10" t="s">
+      <c r="H82" s="9" t="s">
         <v>108</v>
       </c>
       <c r="I82" s="5" t="s">
@@ -7174,34 +7160,34 @@
       <c r="O82" s="5" t="s">
         <v>539</v>
       </c>
-      <c r="P82" s="17">
+      <c r="P82" s="16">
         <v>46196</v>
       </c>
-      <c r="Q82" s="17"/>
-      <c r="R82" s="17">
+      <c r="Q82" s="16"/>
+      <c r="R82" s="16">
         <v>46196</v>
       </c>
-      <c r="S82" s="13" t="s">
+      <c r="S82" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="83" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="10">
+      <c r="A83" s="9">
         <v>81</v>
       </c>
-      <c r="B83" s="27"/>
-      <c r="C83" s="27"/>
-      <c r="D83" s="27"/>
-      <c r="E83" s="10" t="s">
+      <c r="B83" s="24"/>
+      <c r="C83" s="24"/>
+      <c r="D83" s="24"/>
+      <c r="E83" s="9" t="s">
         <v>540</v>
       </c>
-      <c r="F83" s="14" t="s">
+      <c r="F83" s="13" t="s">
         <v>541</v>
       </c>
       <c r="G83" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="H83" s="10" t="s">
+      <c r="H83" s="9" t="s">
         <v>108</v>
       </c>
       <c r="I83" s="5" t="s">
@@ -7225,34 +7211,34 @@
       <c r="O83" s="5" t="s">
         <v>544</v>
       </c>
-      <c r="P83" s="17" t="s">
+      <c r="P83" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="Q83" s="17"/>
-      <c r="R83" s="17" t="s">
+      <c r="Q83" s="16"/>
+      <c r="R83" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="S83" s="13" t="s">
+      <c r="S83" s="12" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="84" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="10">
+      <c r="A84" s="9">
         <v>82</v>
       </c>
-      <c r="B84" s="27"/>
-      <c r="C84" s="27"/>
-      <c r="D84" s="27"/>
-      <c r="E84" s="10" t="s">
+      <c r="B84" s="24"/>
+      <c r="C84" s="24"/>
+      <c r="D84" s="24"/>
+      <c r="E84" s="9" t="s">
         <v>545</v>
       </c>
-      <c r="F84" s="14" t="s">
+      <c r="F84" s="13" t="s">
         <v>546</v>
       </c>
       <c r="G84" s="5" t="s">
         <v>547</v>
       </c>
-      <c r="H84" s="10" t="s">
+      <c r="H84" s="9" t="s">
         <v>108</v>
       </c>
       <c r="I84" s="5" t="s">
@@ -7276,1077 +7262,1136 @@
       <c r="O84" s="5" t="s">
         <v>549</v>
       </c>
-      <c r="P84" s="17" t="s">
+      <c r="P84" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="Q84" s="17"/>
-      <c r="R84" s="17" t="s">
+      <c r="Q84" s="16"/>
+      <c r="R84" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="S84" s="13" t="s">
+      <c r="S84" s="12" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A85" s="10"/>
-      <c r="B85" s="10"/>
-      <c r="C85" s="10"/>
-      <c r="D85" s="10"/>
-      <c r="E85" s="10"/>
-      <c r="F85" s="14"/>
+      <c r="A85" s="9"/>
+      <c r="B85" s="9"/>
+      <c r="C85" s="9"/>
+      <c r="D85" s="9"/>
+      <c r="E85" s="9"/>
+      <c r="F85" s="13"/>
       <c r="G85" s="3"/>
-      <c r="H85" s="10"/>
+      <c r="H85" s="9"/>
       <c r="I85" s="3"/>
-      <c r="J85" s="10"/>
-      <c r="K85" s="10"/>
-      <c r="L85" s="10"/>
-      <c r="M85" s="10"/>
-      <c r="N85" s="10"/>
+      <c r="J85" s="9"/>
+      <c r="K85" s="9"/>
+      <c r="L85" s="9"/>
+      <c r="M85" s="9"/>
+      <c r="N85" s="9"/>
       <c r="O85" s="3"/>
-      <c r="P85" s="17"/>
-      <c r="Q85" s="17"/>
-      <c r="R85" s="17"/>
-      <c r="S85" s="13"/>
+      <c r="P85" s="16"/>
+      <c r="Q85" s="16"/>
+      <c r="R85" s="16"/>
+      <c r="S85" s="12"/>
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A86" s="10"/>
-      <c r="B86" s="10"/>
-      <c r="C86" s="10"/>
-      <c r="D86" s="10"/>
-      <c r="E86" s="10"/>
-      <c r="F86" s="14"/>
+      <c r="A86" s="9"/>
+      <c r="B86" s="9"/>
+      <c r="C86" s="9"/>
+      <c r="D86" s="9"/>
+      <c r="E86" s="9"/>
+      <c r="F86" s="13"/>
       <c r="G86" s="3"/>
-      <c r="H86" s="10"/>
+      <c r="H86" s="9"/>
       <c r="I86" s="3"/>
-      <c r="J86" s="10"/>
-      <c r="K86" s="10"/>
-      <c r="L86" s="10"/>
-      <c r="M86" s="10"/>
-      <c r="N86" s="10"/>
+      <c r="J86" s="9"/>
+      <c r="K86" s="9"/>
+      <c r="L86" s="9"/>
+      <c r="M86" s="9"/>
+      <c r="N86" s="9"/>
       <c r="O86" s="3"/>
-      <c r="P86" s="17"/>
-      <c r="Q86" s="17"/>
-      <c r="R86" s="17"/>
-      <c r="S86" s="13"/>
+      <c r="P86" s="16"/>
+      <c r="Q86" s="16"/>
+      <c r="R86" s="16"/>
+      <c r="S86" s="12"/>
     </row>
     <row r="87" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A87" s="10"/>
-      <c r="B87" s="10"/>
-      <c r="C87" s="10"/>
-      <c r="D87" s="10"/>
-      <c r="E87" s="10"/>
-      <c r="F87" s="14"/>
+      <c r="A87" s="9"/>
+      <c r="B87" s="9"/>
+      <c r="C87" s="9"/>
+      <c r="D87" s="9"/>
+      <c r="E87" s="9"/>
+      <c r="F87" s="13"/>
       <c r="G87" s="3"/>
-      <c r="H87" s="10"/>
+      <c r="H87" s="9"/>
       <c r="I87" s="3"/>
-      <c r="J87" s="10"/>
-      <c r="K87" s="10"/>
-      <c r="L87" s="10"/>
-      <c r="M87" s="10"/>
-      <c r="N87" s="10"/>
+      <c r="J87" s="9"/>
+      <c r="K87" s="9"/>
+      <c r="L87" s="9"/>
+      <c r="M87" s="9"/>
+      <c r="N87" s="9"/>
       <c r="O87" s="3"/>
-      <c r="P87" s="17"/>
-      <c r="Q87" s="17"/>
-      <c r="R87" s="17"/>
-      <c r="S87" s="13"/>
+      <c r="P87" s="16"/>
+      <c r="Q87" s="16"/>
+      <c r="R87" s="16"/>
+      <c r="S87" s="12"/>
     </row>
     <row r="88" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A88" s="10"/>
-      <c r="B88" s="10"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="10"/>
-      <c r="E88" s="10"/>
-      <c r="F88" s="14"/>
+      <c r="A88" s="9"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="9"/>
+      <c r="D88" s="9"/>
+      <c r="E88" s="9"/>
+      <c r="F88" s="13"/>
       <c r="G88" s="3"/>
-      <c r="H88" s="10"/>
+      <c r="H88" s="9"/>
       <c r="I88" s="3"/>
-      <c r="J88" s="10"/>
-      <c r="K88" s="10"/>
-      <c r="L88" s="10"/>
-      <c r="M88" s="10"/>
-      <c r="N88" s="10"/>
+      <c r="J88" s="9"/>
+      <c r="K88" s="9"/>
+      <c r="L88" s="9"/>
+      <c r="M88" s="9"/>
+      <c r="N88" s="9"/>
       <c r="O88" s="3"/>
-      <c r="P88" s="17"/>
-      <c r="Q88" s="17"/>
-      <c r="R88" s="17"/>
-      <c r="S88" s="13"/>
+      <c r="P88" s="16"/>
+      <c r="Q88" s="16"/>
+      <c r="R88" s="16"/>
+      <c r="S88" s="12"/>
     </row>
     <row r="89" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A89" s="10"/>
-      <c r="B89" s="10"/>
-      <c r="C89" s="10"/>
-      <c r="D89" s="10"/>
-      <c r="E89" s="10"/>
-      <c r="F89" s="14"/>
+      <c r="A89" s="9"/>
+      <c r="B89" s="9"/>
+      <c r="C89" s="9"/>
+      <c r="D89" s="9"/>
+      <c r="E89" s="9"/>
+      <c r="F89" s="13"/>
       <c r="G89" s="3"/>
-      <c r="H89" s="10"/>
+      <c r="H89" s="9"/>
       <c r="I89" s="3"/>
-      <c r="J89" s="10"/>
-      <c r="K89" s="10"/>
-      <c r="L89" s="10"/>
-      <c r="M89" s="10"/>
-      <c r="N89" s="10"/>
+      <c r="J89" s="9"/>
+      <c r="K89" s="9"/>
+      <c r="L89" s="9"/>
+      <c r="M89" s="9"/>
+      <c r="N89" s="9"/>
       <c r="O89" s="3"/>
-      <c r="P89" s="17"/>
-      <c r="Q89" s="17"/>
-      <c r="R89" s="17"/>
-      <c r="S89" s="13"/>
+      <c r="P89" s="16"/>
+      <c r="Q89" s="16"/>
+      <c r="R89" s="16"/>
+      <c r="S89" s="12"/>
     </row>
     <row r="90" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A90" s="10"/>
-      <c r="B90" s="10"/>
-      <c r="C90" s="10"/>
-      <c r="D90" s="10"/>
-      <c r="E90" s="10"/>
-      <c r="F90" s="14"/>
+      <c r="A90" s="9"/>
+      <c r="B90" s="9"/>
+      <c r="C90" s="9"/>
+      <c r="D90" s="9"/>
+      <c r="E90" s="9"/>
+      <c r="F90" s="13"/>
       <c r="G90" s="3"/>
-      <c r="H90" s="10"/>
+      <c r="H90" s="9"/>
       <c r="I90" s="3"/>
-      <c r="J90" s="10"/>
-      <c r="K90" s="10"/>
-      <c r="L90" s="10"/>
-      <c r="M90" s="10"/>
-      <c r="N90" s="10"/>
+      <c r="J90" s="9"/>
+      <c r="K90" s="9"/>
+      <c r="L90" s="9"/>
+      <c r="M90" s="9"/>
+      <c r="N90" s="9"/>
       <c r="O90" s="3"/>
-      <c r="P90" s="17"/>
-      <c r="Q90" s="17"/>
-      <c r="R90" s="17"/>
-      <c r="S90" s="13"/>
+      <c r="P90" s="16"/>
+      <c r="Q90" s="16"/>
+      <c r="R90" s="16"/>
+      <c r="S90" s="12"/>
     </row>
     <row r="91" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A91" s="10"/>
-      <c r="B91" s="10"/>
-      <c r="C91" s="10"/>
-      <c r="D91" s="10"/>
-      <c r="E91" s="10"/>
-      <c r="F91" s="14"/>
+      <c r="A91" s="9"/>
+      <c r="B91" s="9"/>
+      <c r="C91" s="9"/>
+      <c r="D91" s="9"/>
+      <c r="E91" s="9"/>
+      <c r="F91" s="13"/>
       <c r="G91" s="3"/>
-      <c r="H91" s="10"/>
+      <c r="H91" s="9"/>
       <c r="I91" s="3"/>
-      <c r="J91" s="10"/>
-      <c r="K91" s="10"/>
-      <c r="L91" s="10"/>
-      <c r="M91" s="10"/>
-      <c r="N91" s="10"/>
+      <c r="J91" s="9"/>
+      <c r="K91" s="9"/>
+      <c r="L91" s="9"/>
+      <c r="M91" s="9"/>
+      <c r="N91" s="9"/>
       <c r="O91" s="3"/>
-      <c r="P91" s="17"/>
-      <c r="Q91" s="17"/>
-      <c r="R91" s="17"/>
-      <c r="S91" s="13"/>
+      <c r="P91" s="16"/>
+      <c r="Q91" s="16"/>
+      <c r="R91" s="16"/>
+      <c r="S91" s="12"/>
     </row>
     <row r="92" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A92" s="10"/>
-      <c r="B92" s="10"/>
-      <c r="C92" s="10"/>
-      <c r="D92" s="10"/>
-      <c r="E92" s="10"/>
-      <c r="F92" s="14"/>
+      <c r="A92" s="9"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="9"/>
+      <c r="D92" s="9"/>
+      <c r="E92" s="9"/>
+      <c r="F92" s="13"/>
       <c r="G92" s="3"/>
-      <c r="H92" s="10"/>
+      <c r="H92" s="9"/>
       <c r="I92" s="3"/>
-      <c r="J92" s="10"/>
-      <c r="K92" s="10"/>
-      <c r="L92" s="10"/>
-      <c r="M92" s="10"/>
-      <c r="N92" s="10"/>
+      <c r="J92" s="9"/>
+      <c r="K92" s="9"/>
+      <c r="L92" s="9"/>
+      <c r="M92" s="9"/>
+      <c r="N92" s="9"/>
       <c r="O92" s="3"/>
-      <c r="P92" s="17"/>
-      <c r="Q92" s="17"/>
-      <c r="R92" s="17"/>
-      <c r="S92" s="13"/>
+      <c r="P92" s="16"/>
+      <c r="Q92" s="16"/>
+      <c r="R92" s="16"/>
+      <c r="S92" s="12"/>
     </row>
     <row r="93" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A93" s="10"/>
-      <c r="B93" s="10"/>
-      <c r="C93" s="10"/>
-      <c r="D93" s="10"/>
-      <c r="E93" s="10"/>
-      <c r="F93" s="14"/>
+      <c r="A93" s="9"/>
+      <c r="B93" s="9"/>
+      <c r="C93" s="9"/>
+      <c r="D93" s="9"/>
+      <c r="E93" s="9"/>
+      <c r="F93" s="13"/>
       <c r="G93" s="3"/>
-      <c r="H93" s="10"/>
+      <c r="H93" s="9"/>
       <c r="I93" s="3"/>
-      <c r="J93" s="10"/>
-      <c r="K93" s="10"/>
-      <c r="L93" s="10"/>
-      <c r="M93" s="10"/>
-      <c r="N93" s="10"/>
+      <c r="J93" s="9"/>
+      <c r="K93" s="9"/>
+      <c r="L93" s="9"/>
+      <c r="M93" s="9"/>
+      <c r="N93" s="9"/>
       <c r="O93" s="3"/>
-      <c r="P93" s="17"/>
-      <c r="Q93" s="17"/>
-      <c r="R93" s="17"/>
-      <c r="S93" s="13"/>
+      <c r="P93" s="16"/>
+      <c r="Q93" s="16"/>
+      <c r="R93" s="16"/>
+      <c r="S93" s="12"/>
     </row>
     <row r="94" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A94" s="10"/>
-      <c r="B94" s="10"/>
-      <c r="C94" s="10"/>
-      <c r="D94" s="10"/>
-      <c r="E94" s="10"/>
-      <c r="F94" s="14"/>
+      <c r="A94" s="9"/>
+      <c r="B94" s="9"/>
+      <c r="C94" s="9"/>
+      <c r="D94" s="9"/>
+      <c r="E94" s="9"/>
+      <c r="F94" s="13"/>
       <c r="G94" s="3"/>
-      <c r="H94" s="10"/>
+      <c r="H94" s="9"/>
       <c r="I94" s="3"/>
-      <c r="J94" s="10"/>
-      <c r="K94" s="10"/>
-      <c r="L94" s="10"/>
-      <c r="M94" s="10"/>
-      <c r="N94" s="10"/>
+      <c r="J94" s="9"/>
+      <c r="K94" s="9"/>
+      <c r="L94" s="9"/>
+      <c r="M94" s="9"/>
+      <c r="N94" s="9"/>
       <c r="O94" s="3"/>
-      <c r="P94" s="17"/>
-      <c r="Q94" s="17"/>
-      <c r="R94" s="17"/>
-      <c r="S94" s="13"/>
+      <c r="P94" s="16"/>
+      <c r="Q94" s="16"/>
+      <c r="R94" s="16"/>
+      <c r="S94" s="12"/>
     </row>
     <row r="95" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A95" s="10"/>
-      <c r="B95" s="10"/>
-      <c r="C95" s="10"/>
-      <c r="D95" s="10"/>
-      <c r="E95" s="10"/>
-      <c r="F95" s="14"/>
+      <c r="A95" s="9"/>
+      <c r="B95" s="9"/>
+      <c r="C95" s="9"/>
+      <c r="D95" s="9"/>
+      <c r="E95" s="9"/>
+      <c r="F95" s="13"/>
       <c r="G95" s="3"/>
-      <c r="H95" s="10"/>
+      <c r="H95" s="9"/>
       <c r="I95" s="3"/>
-      <c r="J95" s="10"/>
-      <c r="K95" s="10"/>
-      <c r="L95" s="10"/>
-      <c r="M95" s="10"/>
-      <c r="N95" s="10"/>
+      <c r="J95" s="9"/>
+      <c r="K95" s="9"/>
+      <c r="L95" s="9"/>
+      <c r="M95" s="9"/>
+      <c r="N95" s="9"/>
       <c r="O95" s="3"/>
-      <c r="P95" s="17"/>
-      <c r="Q95" s="17"/>
-      <c r="R95" s="17"/>
-      <c r="S95" s="13"/>
+      <c r="P95" s="16"/>
+      <c r="Q95" s="16"/>
+      <c r="R95" s="16"/>
+      <c r="S95" s="12"/>
     </row>
     <row r="96" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A96" s="10"/>
-      <c r="B96" s="10"/>
-      <c r="C96" s="10"/>
-      <c r="D96" s="10"/>
-      <c r="E96" s="10"/>
-      <c r="F96" s="14"/>
+      <c r="A96" s="9"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="9"/>
+      <c r="D96" s="9"/>
+      <c r="E96" s="9"/>
+      <c r="F96" s="13"/>
       <c r="G96" s="3"/>
-      <c r="H96" s="10"/>
+      <c r="H96" s="9"/>
       <c r="I96" s="3"/>
-      <c r="J96" s="10"/>
-      <c r="K96" s="10"/>
-      <c r="L96" s="10"/>
-      <c r="M96" s="10"/>
-      <c r="N96" s="10"/>
+      <c r="J96" s="9"/>
+      <c r="K96" s="9"/>
+      <c r="L96" s="9"/>
+      <c r="M96" s="9"/>
+      <c r="N96" s="9"/>
       <c r="O96" s="3"/>
-      <c r="P96" s="17"/>
-      <c r="Q96" s="17"/>
-      <c r="R96" s="17"/>
-      <c r="S96" s="13"/>
+      <c r="P96" s="16"/>
+      <c r="Q96" s="16"/>
+      <c r="R96" s="16"/>
+      <c r="S96" s="12"/>
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A97" s="10"/>
-      <c r="B97" s="10"/>
-      <c r="C97" s="10"/>
-      <c r="D97" s="10"/>
-      <c r="E97" s="10"/>
-      <c r="F97" s="14"/>
+      <c r="A97" s="9"/>
+      <c r="B97" s="9"/>
+      <c r="C97" s="9"/>
+      <c r="D97" s="9"/>
+      <c r="E97" s="9"/>
+      <c r="F97" s="13"/>
       <c r="G97" s="3"/>
-      <c r="H97" s="10"/>
+      <c r="H97" s="9"/>
       <c r="I97" s="3"/>
-      <c r="J97" s="10"/>
-      <c r="K97" s="10"/>
-      <c r="L97" s="10"/>
-      <c r="M97" s="10"/>
-      <c r="N97" s="10"/>
+      <c r="J97" s="9"/>
+      <c r="K97" s="9"/>
+      <c r="L97" s="9"/>
+      <c r="M97" s="9"/>
+      <c r="N97" s="9"/>
       <c r="O97" s="3"/>
-      <c r="P97" s="17"/>
-      <c r="Q97" s="17"/>
-      <c r="R97" s="17"/>
-      <c r="S97" s="13"/>
+      <c r="P97" s="16"/>
+      <c r="Q97" s="16"/>
+      <c r="R97" s="16"/>
+      <c r="S97" s="12"/>
     </row>
     <row r="98" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A98" s="10"/>
-      <c r="B98" s="10"/>
-      <c r="C98" s="10"/>
-      <c r="D98" s="10"/>
-      <c r="E98" s="10"/>
-      <c r="F98" s="14"/>
+      <c r="A98" s="9"/>
+      <c r="B98" s="9"/>
+      <c r="C98" s="9"/>
+      <c r="D98" s="9"/>
+      <c r="E98" s="9"/>
+      <c r="F98" s="13"/>
       <c r="G98" s="3"/>
-      <c r="H98" s="10"/>
+      <c r="H98" s="9"/>
       <c r="I98" s="3"/>
-      <c r="J98" s="10"/>
-      <c r="K98" s="10"/>
-      <c r="L98" s="10"/>
-      <c r="M98" s="10"/>
-      <c r="N98" s="10"/>
+      <c r="J98" s="9"/>
+      <c r="K98" s="9"/>
+      <c r="L98" s="9"/>
+      <c r="M98" s="9"/>
+      <c r="N98" s="9"/>
       <c r="O98" s="3"/>
-      <c r="P98" s="17"/>
-      <c r="Q98" s="17"/>
-      <c r="R98" s="17"/>
-      <c r="S98" s="13"/>
+      <c r="P98" s="16"/>
+      <c r="Q98" s="16"/>
+      <c r="R98" s="16"/>
+      <c r="S98" s="12"/>
     </row>
     <row r="99" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A99" s="10"/>
-      <c r="B99" s="10"/>
-      <c r="C99" s="10"/>
-      <c r="D99" s="10"/>
-      <c r="E99" s="10"/>
-      <c r="F99" s="14"/>
+      <c r="A99" s="9"/>
+      <c r="B99" s="9"/>
+      <c r="C99" s="9"/>
+      <c r="D99" s="9"/>
+      <c r="E99" s="9"/>
+      <c r="F99" s="13"/>
       <c r="G99" s="3"/>
-      <c r="H99" s="10"/>
+      <c r="H99" s="9"/>
       <c r="I99" s="3"/>
-      <c r="J99" s="10"/>
-      <c r="K99" s="10"/>
-      <c r="L99" s="10"/>
-      <c r="M99" s="10"/>
-      <c r="N99" s="10"/>
+      <c r="J99" s="9"/>
+      <c r="K99" s="9"/>
+      <c r="L99" s="9"/>
+      <c r="M99" s="9"/>
+      <c r="N99" s="9"/>
       <c r="O99" s="3"/>
-      <c r="P99" s="17"/>
-      <c r="Q99" s="17"/>
-      <c r="R99" s="17"/>
-      <c r="S99" s="13"/>
+      <c r="P99" s="16"/>
+      <c r="Q99" s="16"/>
+      <c r="R99" s="16"/>
+      <c r="S99" s="12"/>
     </row>
     <row r="100" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A100" s="10"/>
-      <c r="B100" s="10"/>
-      <c r="C100" s="10"/>
-      <c r="D100" s="10"/>
-      <c r="E100" s="10"/>
-      <c r="F100" s="14"/>
+      <c r="A100" s="9"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="9"/>
+      <c r="D100" s="9"/>
+      <c r="E100" s="9"/>
+      <c r="F100" s="13"/>
       <c r="G100" s="3"/>
-      <c r="H100" s="10"/>
+      <c r="H100" s="9"/>
       <c r="I100" s="3"/>
-      <c r="J100" s="10"/>
-      <c r="K100" s="10"/>
-      <c r="L100" s="10"/>
-      <c r="M100" s="10"/>
-      <c r="N100" s="10"/>
+      <c r="J100" s="9"/>
+      <c r="K100" s="9"/>
+      <c r="L100" s="9"/>
+      <c r="M100" s="9"/>
+      <c r="N100" s="9"/>
       <c r="O100" s="3"/>
-      <c r="P100" s="17"/>
-      <c r="Q100" s="17"/>
-      <c r="R100" s="17"/>
-      <c r="S100" s="13"/>
+      <c r="P100" s="16"/>
+      <c r="Q100" s="16"/>
+      <c r="R100" s="16"/>
+      <c r="S100" s="12"/>
     </row>
     <row r="101" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A101" s="10"/>
-      <c r="B101" s="10"/>
-      <c r="C101" s="10"/>
-      <c r="D101" s="10"/>
-      <c r="E101" s="10"/>
-      <c r="F101" s="14"/>
+      <c r="A101" s="9"/>
+      <c r="B101" s="9"/>
+      <c r="C101" s="9"/>
+      <c r="D101" s="9"/>
+      <c r="E101" s="9"/>
+      <c r="F101" s="13"/>
       <c r="G101" s="3"/>
-      <c r="H101" s="10"/>
+      <c r="H101" s="9"/>
       <c r="I101" s="3"/>
-      <c r="J101" s="10"/>
-      <c r="K101" s="10"/>
-      <c r="L101" s="10"/>
-      <c r="M101" s="10"/>
-      <c r="N101" s="10"/>
+      <c r="J101" s="9"/>
+      <c r="K101" s="9"/>
+      <c r="L101" s="9"/>
+      <c r="M101" s="9"/>
+      <c r="N101" s="9"/>
       <c r="O101" s="3"/>
-      <c r="P101" s="17"/>
-      <c r="Q101" s="17"/>
-      <c r="R101" s="17"/>
-      <c r="S101" s="13"/>
+      <c r="P101" s="16"/>
+      <c r="Q101" s="16"/>
+      <c r="R101" s="16"/>
+      <c r="S101" s="12"/>
     </row>
     <row r="102" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A102" s="10"/>
-      <c r="B102" s="10"/>
-      <c r="C102" s="10"/>
-      <c r="D102" s="10"/>
-      <c r="E102" s="10"/>
-      <c r="F102" s="14"/>
+      <c r="A102" s="9"/>
+      <c r="B102" s="9"/>
+      <c r="C102" s="9"/>
+      <c r="D102" s="9"/>
+      <c r="E102" s="9"/>
+      <c r="F102" s="13"/>
       <c r="G102" s="3"/>
-      <c r="H102" s="10"/>
+      <c r="H102" s="9"/>
       <c r="I102" s="3"/>
-      <c r="J102" s="10"/>
-      <c r="K102" s="10"/>
-      <c r="L102" s="10"/>
-      <c r="M102" s="10"/>
-      <c r="N102" s="10"/>
+      <c r="J102" s="9"/>
+      <c r="K102" s="9"/>
+      <c r="L102" s="9"/>
+      <c r="M102" s="9"/>
+      <c r="N102" s="9"/>
       <c r="O102" s="3"/>
-      <c r="P102" s="17"/>
-      <c r="Q102" s="17"/>
-      <c r="R102" s="17"/>
-      <c r="S102" s="13"/>
+      <c r="P102" s="16"/>
+      <c r="Q102" s="16"/>
+      <c r="R102" s="16"/>
+      <c r="S102" s="12"/>
     </row>
     <row r="103" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A103" s="10"/>
-      <c r="B103" s="10"/>
-      <c r="C103" s="10"/>
-      <c r="D103" s="10"/>
-      <c r="E103" s="10"/>
-      <c r="F103" s="14"/>
+      <c r="A103" s="9"/>
+      <c r="B103" s="9"/>
+      <c r="C103" s="9"/>
+      <c r="D103" s="9"/>
+      <c r="E103" s="9"/>
+      <c r="F103" s="13"/>
       <c r="G103" s="3"/>
-      <c r="H103" s="10"/>
+      <c r="H103" s="9"/>
       <c r="I103" s="3"/>
-      <c r="J103" s="10"/>
-      <c r="K103" s="10"/>
-      <c r="L103" s="10"/>
-      <c r="M103" s="10"/>
-      <c r="N103" s="10"/>
+      <c r="J103" s="9"/>
+      <c r="K103" s="9"/>
+      <c r="L103" s="9"/>
+      <c r="M103" s="9"/>
+      <c r="N103" s="9"/>
       <c r="O103" s="3"/>
-      <c r="P103" s="17"/>
-      <c r="Q103" s="17"/>
-      <c r="R103" s="17"/>
-      <c r="S103" s="13"/>
+      <c r="P103" s="16"/>
+      <c r="Q103" s="16"/>
+      <c r="R103" s="16"/>
+      <c r="S103" s="12"/>
     </row>
     <row r="104" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A104" s="10"/>
-      <c r="B104" s="10"/>
-      <c r="C104" s="10"/>
-      <c r="D104" s="10"/>
-      <c r="E104" s="10"/>
-      <c r="F104" s="14"/>
+      <c r="A104" s="9"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="9"/>
+      <c r="D104" s="9"/>
+      <c r="E104" s="9"/>
+      <c r="F104" s="13"/>
       <c r="G104" s="3"/>
-      <c r="H104" s="10"/>
+      <c r="H104" s="9"/>
       <c r="I104" s="3"/>
-      <c r="J104" s="10"/>
-      <c r="K104" s="10"/>
-      <c r="L104" s="10"/>
-      <c r="M104" s="10"/>
-      <c r="N104" s="10"/>
+      <c r="J104" s="9"/>
+      <c r="K104" s="9"/>
+      <c r="L104" s="9"/>
+      <c r="M104" s="9"/>
+      <c r="N104" s="9"/>
       <c r="O104" s="3"/>
-      <c r="P104" s="17"/>
-      <c r="Q104" s="17"/>
-      <c r="R104" s="17"/>
-      <c r="S104" s="13"/>
+      <c r="P104" s="16"/>
+      <c r="Q104" s="16"/>
+      <c r="R104" s="16"/>
+      <c r="S104" s="12"/>
     </row>
     <row r="105" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A105" s="10"/>
-      <c r="B105" s="10"/>
-      <c r="C105" s="10"/>
-      <c r="D105" s="10"/>
-      <c r="E105" s="10"/>
-      <c r="F105" s="14"/>
+      <c r="A105" s="9"/>
+      <c r="B105" s="9"/>
+      <c r="C105" s="9"/>
+      <c r="D105" s="9"/>
+      <c r="E105" s="9"/>
+      <c r="F105" s="13"/>
       <c r="G105" s="3"/>
-      <c r="H105" s="10"/>
+      <c r="H105" s="9"/>
       <c r="I105" s="3"/>
-      <c r="J105" s="10"/>
-      <c r="K105" s="10"/>
-      <c r="L105" s="10"/>
-      <c r="M105" s="10"/>
-      <c r="N105" s="10"/>
+      <c r="J105" s="9"/>
+      <c r="K105" s="9"/>
+      <c r="L105" s="9"/>
+      <c r="M105" s="9"/>
+      <c r="N105" s="9"/>
       <c r="O105" s="3"/>
-      <c r="P105" s="17"/>
-      <c r="Q105" s="17"/>
-      <c r="R105" s="17"/>
-      <c r="S105" s="13"/>
+      <c r="P105" s="16"/>
+      <c r="Q105" s="16"/>
+      <c r="R105" s="16"/>
+      <c r="S105" s="12"/>
     </row>
     <row r="106" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A106" s="10"/>
-      <c r="B106" s="10"/>
-      <c r="C106" s="10"/>
-      <c r="D106" s="10"/>
-      <c r="E106" s="10"/>
-      <c r="F106" s="14"/>
+      <c r="A106" s="9"/>
+      <c r="B106" s="9"/>
+      <c r="C106" s="9"/>
+      <c r="D106" s="9"/>
+      <c r="E106" s="9"/>
+      <c r="F106" s="13"/>
       <c r="G106" s="3"/>
-      <c r="H106" s="10"/>
+      <c r="H106" s="9"/>
       <c r="I106" s="3"/>
-      <c r="J106" s="10"/>
-      <c r="K106" s="10"/>
-      <c r="L106" s="10"/>
-      <c r="M106" s="10"/>
-      <c r="N106" s="10"/>
+      <c r="J106" s="9"/>
+      <c r="K106" s="9"/>
+      <c r="L106" s="9"/>
+      <c r="M106" s="9"/>
+      <c r="N106" s="9"/>
       <c r="O106" s="3"/>
-      <c r="P106" s="17"/>
-      <c r="Q106" s="17"/>
-      <c r="R106" s="17"/>
-      <c r="S106" s="13"/>
+      <c r="P106" s="16"/>
+      <c r="Q106" s="16"/>
+      <c r="R106" s="16"/>
+      <c r="S106" s="12"/>
     </row>
     <row r="107" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A107" s="10"/>
-      <c r="B107" s="10"/>
-      <c r="C107" s="10"/>
-      <c r="D107" s="10"/>
-      <c r="E107" s="10"/>
-      <c r="F107" s="14"/>
+      <c r="A107" s="9"/>
+      <c r="B107" s="9"/>
+      <c r="C107" s="9"/>
+      <c r="D107" s="9"/>
+      <c r="E107" s="9"/>
+      <c r="F107" s="13"/>
       <c r="G107" s="3"/>
-      <c r="H107" s="10"/>
+      <c r="H107" s="9"/>
       <c r="I107" s="3"/>
-      <c r="J107" s="10"/>
-      <c r="K107" s="10"/>
-      <c r="L107" s="10"/>
-      <c r="M107" s="10"/>
-      <c r="N107" s="10"/>
+      <c r="J107" s="9"/>
+      <c r="K107" s="9"/>
+      <c r="L107" s="9"/>
+      <c r="M107" s="9"/>
+      <c r="N107" s="9"/>
       <c r="O107" s="3"/>
-      <c r="P107" s="17"/>
-      <c r="Q107" s="17"/>
-      <c r="R107" s="17"/>
-      <c r="S107" s="13"/>
+      <c r="P107" s="16"/>
+      <c r="Q107" s="16"/>
+      <c r="R107" s="16"/>
+      <c r="S107" s="12"/>
     </row>
     <row r="108" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A108" s="10"/>
-      <c r="B108" s="10"/>
-      <c r="C108" s="10"/>
-      <c r="D108" s="10"/>
-      <c r="E108" s="10"/>
-      <c r="F108" s="14"/>
+      <c r="A108" s="9"/>
+      <c r="B108" s="9"/>
+      <c r="C108" s="9"/>
+      <c r="D108" s="9"/>
+      <c r="E108" s="9"/>
+      <c r="F108" s="13"/>
       <c r="G108" s="3"/>
-      <c r="H108" s="10"/>
+      <c r="H108" s="9"/>
       <c r="I108" s="3"/>
-      <c r="J108" s="10"/>
-      <c r="K108" s="10"/>
-      <c r="L108" s="10"/>
-      <c r="M108" s="10"/>
-      <c r="N108" s="10"/>
+      <c r="J108" s="9"/>
+      <c r="K108" s="9"/>
+      <c r="L108" s="9"/>
+      <c r="M108" s="9"/>
+      <c r="N108" s="9"/>
       <c r="O108" s="3"/>
-      <c r="P108" s="17"/>
-      <c r="Q108" s="17"/>
-      <c r="R108" s="17"/>
-      <c r="S108" s="13"/>
+      <c r="P108" s="16"/>
+      <c r="Q108" s="16"/>
+      <c r="R108" s="16"/>
+      <c r="S108" s="12"/>
     </row>
     <row r="109" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A109" s="10"/>
-      <c r="B109" s="10"/>
-      <c r="C109" s="10"/>
-      <c r="D109" s="10"/>
-      <c r="E109" s="10"/>
-      <c r="F109" s="14"/>
+      <c r="A109" s="9"/>
+      <c r="B109" s="9"/>
+      <c r="C109" s="9"/>
+      <c r="D109" s="9"/>
+      <c r="E109" s="9"/>
+      <c r="F109" s="13"/>
       <c r="G109" s="3"/>
-      <c r="H109" s="10"/>
+      <c r="H109" s="9"/>
       <c r="I109" s="3"/>
-      <c r="J109" s="10"/>
-      <c r="K109" s="10"/>
-      <c r="L109" s="10"/>
-      <c r="M109" s="10"/>
-      <c r="N109" s="10"/>
+      <c r="J109" s="9"/>
+      <c r="K109" s="9"/>
+      <c r="L109" s="9"/>
+      <c r="M109" s="9"/>
+      <c r="N109" s="9"/>
       <c r="O109" s="3"/>
-      <c r="P109" s="17"/>
-      <c r="Q109" s="17"/>
-      <c r="R109" s="17"/>
-      <c r="S109" s="13"/>
+      <c r="P109" s="16"/>
+      <c r="Q109" s="16"/>
+      <c r="R109" s="16"/>
+      <c r="S109" s="12"/>
     </row>
     <row r="110" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A110" s="10"/>
-      <c r="B110" s="10"/>
-      <c r="C110" s="10"/>
-      <c r="D110" s="10"/>
-      <c r="E110" s="10"/>
-      <c r="F110" s="14"/>
+      <c r="A110" s="9"/>
+      <c r="B110" s="9"/>
+      <c r="C110" s="9"/>
+      <c r="D110" s="9"/>
+      <c r="E110" s="9"/>
+      <c r="F110" s="13"/>
       <c r="G110" s="3"/>
-      <c r="H110" s="10"/>
+      <c r="H110" s="9"/>
       <c r="I110" s="3"/>
-      <c r="J110" s="10"/>
-      <c r="K110" s="10"/>
-      <c r="L110" s="10"/>
-      <c r="M110" s="10"/>
-      <c r="N110" s="10"/>
+      <c r="J110" s="9"/>
+      <c r="K110" s="9"/>
+      <c r="L110" s="9"/>
+      <c r="M110" s="9"/>
+      <c r="N110" s="9"/>
       <c r="O110" s="3"/>
-      <c r="P110" s="17"/>
-      <c r="Q110" s="17"/>
-      <c r="R110" s="17"/>
-      <c r="S110" s="13"/>
+      <c r="P110" s="16"/>
+      <c r="Q110" s="16"/>
+      <c r="R110" s="16"/>
+      <c r="S110" s="12"/>
     </row>
     <row r="111" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A111" s="10"/>
-      <c r="B111" s="10"/>
-      <c r="C111" s="10"/>
-      <c r="D111" s="10"/>
-      <c r="E111" s="10"/>
-      <c r="F111" s="14"/>
+      <c r="A111" s="9"/>
+      <c r="B111" s="9"/>
+      <c r="C111" s="9"/>
+      <c r="D111" s="9"/>
+      <c r="E111" s="9"/>
+      <c r="F111" s="13"/>
       <c r="G111" s="3"/>
-      <c r="H111" s="10"/>
+      <c r="H111" s="9"/>
       <c r="I111" s="3"/>
-      <c r="J111" s="10"/>
-      <c r="K111" s="10"/>
-      <c r="L111" s="10"/>
-      <c r="M111" s="10"/>
-      <c r="N111" s="10"/>
+      <c r="J111" s="9"/>
+      <c r="K111" s="9"/>
+      <c r="L111" s="9"/>
+      <c r="M111" s="9"/>
+      <c r="N111" s="9"/>
       <c r="O111" s="3"/>
-      <c r="P111" s="17"/>
-      <c r="Q111" s="17"/>
-      <c r="R111" s="17"/>
-      <c r="S111" s="13"/>
+      <c r="P111" s="16"/>
+      <c r="Q111" s="16"/>
+      <c r="R111" s="16"/>
+      <c r="S111" s="12"/>
     </row>
     <row r="112" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A112" s="10"/>
-      <c r="B112" s="10"/>
-      <c r="C112" s="10"/>
-      <c r="D112" s="10"/>
-      <c r="E112" s="10"/>
-      <c r="F112" s="14"/>
+      <c r="A112" s="9"/>
+      <c r="B112" s="9"/>
+      <c r="C112" s="9"/>
+      <c r="D112" s="9"/>
+      <c r="E112" s="9"/>
+      <c r="F112" s="13"/>
       <c r="G112" s="3"/>
-      <c r="H112" s="10"/>
+      <c r="H112" s="9"/>
       <c r="I112" s="3"/>
-      <c r="J112" s="10"/>
-      <c r="K112" s="10"/>
-      <c r="L112" s="10"/>
-      <c r="M112" s="10"/>
-      <c r="N112" s="10"/>
+      <c r="J112" s="9"/>
+      <c r="K112" s="9"/>
+      <c r="L112" s="9"/>
+      <c r="M112" s="9"/>
+      <c r="N112" s="9"/>
       <c r="O112" s="3"/>
-      <c r="P112" s="17"/>
-      <c r="Q112" s="17"/>
-      <c r="R112" s="17"/>
-      <c r="S112" s="13"/>
+      <c r="P112" s="16"/>
+      <c r="Q112" s="16"/>
+      <c r="R112" s="16"/>
+      <c r="S112" s="12"/>
     </row>
     <row r="113" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A113" s="10"/>
-      <c r="B113" s="10"/>
-      <c r="C113" s="10"/>
-      <c r="D113" s="10"/>
-      <c r="E113" s="10"/>
-      <c r="F113" s="14"/>
+      <c r="A113" s="9"/>
+      <c r="B113" s="9"/>
+      <c r="C113" s="9"/>
+      <c r="D113" s="9"/>
+      <c r="E113" s="9"/>
+      <c r="F113" s="13"/>
       <c r="G113" s="3"/>
-      <c r="H113" s="10"/>
+      <c r="H113" s="9"/>
       <c r="I113" s="3"/>
-      <c r="J113" s="10"/>
-      <c r="K113" s="10"/>
-      <c r="L113" s="10"/>
-      <c r="M113" s="10"/>
-      <c r="N113" s="10"/>
+      <c r="J113" s="9"/>
+      <c r="K113" s="9"/>
+      <c r="L113" s="9"/>
+      <c r="M113" s="9"/>
+      <c r="N113" s="9"/>
       <c r="O113" s="3"/>
-      <c r="P113" s="17"/>
-      <c r="Q113" s="17"/>
-      <c r="R113" s="17"/>
-      <c r="S113" s="13"/>
+      <c r="P113" s="16"/>
+      <c r="Q113" s="16"/>
+      <c r="R113" s="16"/>
+      <c r="S113" s="12"/>
     </row>
     <row r="114" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A114" s="10"/>
-      <c r="B114" s="10"/>
-      <c r="C114" s="10"/>
-      <c r="D114" s="10"/>
-      <c r="E114" s="10"/>
-      <c r="F114" s="14"/>
+      <c r="A114" s="9"/>
+      <c r="B114" s="9"/>
+      <c r="C114" s="9"/>
+      <c r="D114" s="9"/>
+      <c r="E114" s="9"/>
+      <c r="F114" s="13"/>
       <c r="G114" s="3"/>
-      <c r="H114" s="10"/>
+      <c r="H114" s="9"/>
       <c r="I114" s="3"/>
-      <c r="J114" s="10"/>
-      <c r="K114" s="10"/>
-      <c r="L114" s="10"/>
-      <c r="M114" s="10"/>
-      <c r="N114" s="10"/>
+      <c r="J114" s="9"/>
+      <c r="K114" s="9"/>
+      <c r="L114" s="9"/>
+      <c r="M114" s="9"/>
+      <c r="N114" s="9"/>
       <c r="O114" s="3"/>
-      <c r="P114" s="17"/>
-      <c r="Q114" s="17"/>
-      <c r="R114" s="17"/>
-      <c r="S114" s="13"/>
+      <c r="P114" s="16"/>
+      <c r="Q114" s="16"/>
+      <c r="R114" s="16"/>
+      <c r="S114" s="12"/>
     </row>
     <row r="115" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A115" s="10"/>
-      <c r="B115" s="10"/>
-      <c r="C115" s="10"/>
-      <c r="D115" s="10"/>
-      <c r="E115" s="10"/>
-      <c r="F115" s="14"/>
+      <c r="A115" s="9"/>
+      <c r="B115" s="9"/>
+      <c r="C115" s="9"/>
+      <c r="D115" s="9"/>
+      <c r="E115" s="9"/>
+      <c r="F115" s="13"/>
       <c r="G115" s="3"/>
-      <c r="H115" s="10"/>
+      <c r="H115" s="9"/>
       <c r="I115" s="3"/>
-      <c r="J115" s="10"/>
-      <c r="K115" s="10"/>
-      <c r="L115" s="10"/>
-      <c r="M115" s="10"/>
-      <c r="N115" s="10"/>
+      <c r="J115" s="9"/>
+      <c r="K115" s="9"/>
+      <c r="L115" s="9"/>
+      <c r="M115" s="9"/>
+      <c r="N115" s="9"/>
       <c r="O115" s="3"/>
-      <c r="P115" s="17"/>
-      <c r="Q115" s="17"/>
-      <c r="R115" s="17"/>
-      <c r="S115" s="13"/>
+      <c r="P115" s="16"/>
+      <c r="Q115" s="16"/>
+      <c r="R115" s="16"/>
+      <c r="S115" s="12"/>
     </row>
     <row r="116" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A116" s="10"/>
-      <c r="B116" s="10"/>
-      <c r="C116" s="10"/>
-      <c r="D116" s="10"/>
-      <c r="E116" s="10"/>
-      <c r="F116" s="14"/>
+      <c r="A116" s="9"/>
+      <c r="B116" s="9"/>
+      <c r="C116" s="9"/>
+      <c r="D116" s="9"/>
+      <c r="E116" s="9"/>
+      <c r="F116" s="13"/>
       <c r="G116" s="3"/>
-      <c r="H116" s="10"/>
+      <c r="H116" s="9"/>
       <c r="I116" s="3"/>
-      <c r="J116" s="10"/>
-      <c r="K116" s="10"/>
-      <c r="L116" s="10"/>
-      <c r="M116" s="10"/>
-      <c r="N116" s="10"/>
+      <c r="J116" s="9"/>
+      <c r="K116" s="9"/>
+      <c r="L116" s="9"/>
+      <c r="M116" s="9"/>
+      <c r="N116" s="9"/>
       <c r="O116" s="3"/>
-      <c r="P116" s="17"/>
-      <c r="Q116" s="17"/>
-      <c r="R116" s="17"/>
-      <c r="S116" s="13"/>
+      <c r="P116" s="16"/>
+      <c r="Q116" s="16"/>
+      <c r="R116" s="16"/>
+      <c r="S116" s="12"/>
     </row>
     <row r="117" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A117" s="10"/>
-      <c r="B117" s="10"/>
-      <c r="C117" s="10"/>
-      <c r="D117" s="10"/>
-      <c r="E117" s="10"/>
-      <c r="F117" s="14"/>
+      <c r="A117" s="9"/>
+      <c r="B117" s="9"/>
+      <c r="C117" s="9"/>
+      <c r="D117" s="9"/>
+      <c r="E117" s="9"/>
+      <c r="F117" s="13"/>
       <c r="G117" s="3"/>
-      <c r="H117" s="10"/>
+      <c r="H117" s="9"/>
       <c r="I117" s="3"/>
-      <c r="J117" s="10"/>
-      <c r="K117" s="10"/>
-      <c r="L117" s="10"/>
-      <c r="M117" s="10"/>
-      <c r="N117" s="10"/>
+      <c r="J117" s="9"/>
+      <c r="K117" s="9"/>
+      <c r="L117" s="9"/>
+      <c r="M117" s="9"/>
+      <c r="N117" s="9"/>
       <c r="O117" s="3"/>
-      <c r="P117" s="17"/>
-      <c r="Q117" s="17"/>
-      <c r="R117" s="17"/>
-      <c r="S117" s="13"/>
+      <c r="P117" s="16"/>
+      <c r="Q117" s="16"/>
+      <c r="R117" s="16"/>
+      <c r="S117" s="12"/>
     </row>
     <row r="118" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A118" s="10"/>
-      <c r="B118" s="10"/>
-      <c r="C118" s="10"/>
-      <c r="D118" s="10"/>
-      <c r="E118" s="10"/>
-      <c r="F118" s="14"/>
+      <c r="A118" s="9"/>
+      <c r="B118" s="9"/>
+      <c r="C118" s="9"/>
+      <c r="D118" s="9"/>
+      <c r="E118" s="9"/>
+      <c r="F118" s="13"/>
       <c r="G118" s="3"/>
-      <c r="H118" s="10"/>
+      <c r="H118" s="9"/>
       <c r="I118" s="3"/>
-      <c r="J118" s="10"/>
-      <c r="K118" s="10"/>
-      <c r="L118" s="10"/>
-      <c r="M118" s="10"/>
-      <c r="N118" s="10"/>
+      <c r="J118" s="9"/>
+      <c r="K118" s="9"/>
+      <c r="L118" s="9"/>
+      <c r="M118" s="9"/>
+      <c r="N118" s="9"/>
       <c r="O118" s="3"/>
-      <c r="P118" s="17"/>
-      <c r="Q118" s="17"/>
-      <c r="R118" s="17"/>
-      <c r="S118" s="13"/>
+      <c r="P118" s="16"/>
+      <c r="Q118" s="16"/>
+      <c r="R118" s="16"/>
+      <c r="S118" s="12"/>
     </row>
     <row r="119" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A119" s="10"/>
-      <c r="B119" s="10"/>
-      <c r="C119" s="10"/>
-      <c r="D119" s="10"/>
-      <c r="E119" s="10"/>
-      <c r="F119" s="14"/>
+      <c r="A119" s="9"/>
+      <c r="B119" s="9"/>
+      <c r="C119" s="9"/>
+      <c r="D119" s="9"/>
+      <c r="E119" s="9"/>
+      <c r="F119" s="13"/>
       <c r="G119" s="3"/>
-      <c r="H119" s="10"/>
+      <c r="H119" s="9"/>
       <c r="I119" s="3"/>
-      <c r="J119" s="10"/>
-      <c r="K119" s="10"/>
-      <c r="L119" s="10"/>
-      <c r="M119" s="10"/>
-      <c r="N119" s="10"/>
+      <c r="J119" s="9"/>
+      <c r="K119" s="9"/>
+      <c r="L119" s="9"/>
+      <c r="M119" s="9"/>
+      <c r="N119" s="9"/>
       <c r="O119" s="3"/>
-      <c r="P119" s="17"/>
-      <c r="Q119" s="17"/>
-      <c r="R119" s="17"/>
-      <c r="S119" s="13"/>
+      <c r="P119" s="16"/>
+      <c r="Q119" s="16"/>
+      <c r="R119" s="16"/>
+      <c r="S119" s="12"/>
     </row>
     <row r="120" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A120" s="10"/>
-      <c r="B120" s="10"/>
-      <c r="C120" s="10"/>
-      <c r="D120" s="10"/>
-      <c r="E120" s="10"/>
-      <c r="F120" s="14"/>
+      <c r="A120" s="9"/>
+      <c r="B120" s="9"/>
+      <c r="C120" s="9"/>
+      <c r="D120" s="9"/>
+      <c r="E120" s="9"/>
+      <c r="F120" s="13"/>
       <c r="G120" s="3"/>
-      <c r="H120" s="10"/>
+      <c r="H120" s="9"/>
       <c r="I120" s="3"/>
-      <c r="J120" s="10"/>
-      <c r="K120" s="10"/>
-      <c r="L120" s="10"/>
-      <c r="M120" s="10"/>
-      <c r="N120" s="10"/>
+      <c r="J120" s="9"/>
+      <c r="K120" s="9"/>
+      <c r="L120" s="9"/>
+      <c r="M120" s="9"/>
+      <c r="N120" s="9"/>
       <c r="O120" s="3"/>
-      <c r="P120" s="17"/>
-      <c r="Q120" s="17"/>
-      <c r="R120" s="17"/>
-      <c r="S120" s="13"/>
+      <c r="P120" s="16"/>
+      <c r="Q120" s="16"/>
+      <c r="R120" s="16"/>
+      <c r="S120" s="12"/>
     </row>
     <row r="121" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A121" s="10"/>
-      <c r="B121" s="10"/>
-      <c r="C121" s="10"/>
-      <c r="D121" s="10"/>
-      <c r="E121" s="10"/>
-      <c r="F121" s="14"/>
+      <c r="A121" s="9"/>
+      <c r="B121" s="9"/>
+      <c r="C121" s="9"/>
+      <c r="D121" s="9"/>
+      <c r="E121" s="9"/>
+      <c r="F121" s="13"/>
       <c r="G121" s="3"/>
-      <c r="H121" s="10"/>
+      <c r="H121" s="9"/>
       <c r="I121" s="3"/>
-      <c r="J121" s="10"/>
-      <c r="K121" s="10"/>
-      <c r="L121" s="10"/>
-      <c r="M121" s="10"/>
-      <c r="N121" s="10"/>
+      <c r="J121" s="9"/>
+      <c r="K121" s="9"/>
+      <c r="L121" s="9"/>
+      <c r="M121" s="9"/>
+      <c r="N121" s="9"/>
       <c r="O121" s="3"/>
-      <c r="P121" s="17"/>
-      <c r="Q121" s="17"/>
-      <c r="R121" s="17"/>
-      <c r="S121" s="13"/>
+      <c r="P121" s="16"/>
+      <c r="Q121" s="16"/>
+      <c r="R121" s="16"/>
+      <c r="S121" s="12"/>
     </row>
     <row r="122" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A122" s="10"/>
-      <c r="B122" s="10"/>
-      <c r="C122" s="10"/>
-      <c r="D122" s="10"/>
-      <c r="E122" s="10"/>
-      <c r="F122" s="14"/>
+      <c r="A122" s="9"/>
+      <c r="B122" s="9"/>
+      <c r="C122" s="9"/>
+      <c r="D122" s="9"/>
+      <c r="E122" s="9"/>
+      <c r="F122" s="13"/>
       <c r="G122" s="3"/>
-      <c r="H122" s="10"/>
+      <c r="H122" s="9"/>
       <c r="I122" s="3"/>
-      <c r="J122" s="10"/>
-      <c r="K122" s="10"/>
-      <c r="L122" s="10"/>
-      <c r="M122" s="10"/>
-      <c r="N122" s="10"/>
+      <c r="J122" s="9"/>
+      <c r="K122" s="9"/>
+      <c r="L122" s="9"/>
+      <c r="M122" s="9"/>
+      <c r="N122" s="9"/>
       <c r="O122" s="3"/>
-      <c r="P122" s="17"/>
-      <c r="Q122" s="17"/>
-      <c r="R122" s="17"/>
-      <c r="S122" s="13"/>
+      <c r="P122" s="16"/>
+      <c r="Q122" s="16"/>
+      <c r="R122" s="16"/>
+      <c r="S122" s="12"/>
     </row>
     <row r="123" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A123" s="10"/>
-      <c r="B123" s="10"/>
-      <c r="C123" s="10"/>
-      <c r="D123" s="10"/>
-      <c r="E123" s="10"/>
-      <c r="F123" s="14"/>
+      <c r="A123" s="9"/>
+      <c r="B123" s="9"/>
+      <c r="C123" s="9"/>
+      <c r="D123" s="9"/>
+      <c r="E123" s="9"/>
+      <c r="F123" s="13"/>
       <c r="G123" s="3"/>
-      <c r="H123" s="10"/>
+      <c r="H123" s="9"/>
       <c r="I123" s="3"/>
-      <c r="J123" s="10"/>
-      <c r="K123" s="10"/>
-      <c r="L123" s="10"/>
-      <c r="M123" s="10"/>
-      <c r="N123" s="10"/>
+      <c r="J123" s="9"/>
+      <c r="K123" s="9"/>
+      <c r="L123" s="9"/>
+      <c r="M123" s="9"/>
+      <c r="N123" s="9"/>
       <c r="O123" s="3"/>
-      <c r="P123" s="17"/>
-      <c r="Q123" s="17"/>
-      <c r="R123" s="17"/>
-      <c r="S123" s="13"/>
+      <c r="P123" s="16"/>
+      <c r="Q123" s="16"/>
+      <c r="R123" s="16"/>
+      <c r="S123" s="12"/>
     </row>
     <row r="124" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A124" s="10"/>
-      <c r="B124" s="10"/>
-      <c r="C124" s="10"/>
-      <c r="D124" s="10"/>
-      <c r="E124" s="10"/>
-      <c r="F124" s="14"/>
+      <c r="A124" s="9"/>
+      <c r="B124" s="9"/>
+      <c r="C124" s="9"/>
+      <c r="D124" s="9"/>
+      <c r="E124" s="9"/>
+      <c r="F124" s="13"/>
       <c r="G124" s="3"/>
-      <c r="H124" s="10"/>
+      <c r="H124" s="9"/>
       <c r="I124" s="3"/>
-      <c r="J124" s="10"/>
-      <c r="K124" s="10"/>
-      <c r="L124" s="10"/>
-      <c r="M124" s="10"/>
-      <c r="N124" s="10"/>
+      <c r="J124" s="9"/>
+      <c r="K124" s="9"/>
+      <c r="L124" s="9"/>
+      <c r="M124" s="9"/>
+      <c r="N124" s="9"/>
       <c r="O124" s="3"/>
-      <c r="P124" s="17"/>
-      <c r="Q124" s="17"/>
-      <c r="R124" s="17"/>
-      <c r="S124" s="13"/>
+      <c r="P124" s="16"/>
+      <c r="Q124" s="16"/>
+      <c r="R124" s="16"/>
+      <c r="S124" s="12"/>
     </row>
     <row r="125" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A125" s="10"/>
-      <c r="B125" s="10"/>
-      <c r="C125" s="10"/>
-      <c r="D125" s="10"/>
-      <c r="E125" s="10"/>
-      <c r="F125" s="14"/>
+      <c r="A125" s="9"/>
+      <c r="B125" s="9"/>
+      <c r="C125" s="9"/>
+      <c r="D125" s="9"/>
+      <c r="E125" s="9"/>
+      <c r="F125" s="13"/>
       <c r="G125" s="3"/>
-      <c r="H125" s="10"/>
+      <c r="H125" s="9"/>
       <c r="I125" s="3"/>
-      <c r="J125" s="10"/>
-      <c r="K125" s="10"/>
-      <c r="L125" s="10"/>
-      <c r="M125" s="10"/>
-      <c r="N125" s="10"/>
+      <c r="J125" s="9"/>
+      <c r="K125" s="9"/>
+      <c r="L125" s="9"/>
+      <c r="M125" s="9"/>
+      <c r="N125" s="9"/>
       <c r="O125" s="3"/>
-      <c r="P125" s="17"/>
-      <c r="Q125" s="17"/>
-      <c r="R125" s="17"/>
-      <c r="S125" s="13"/>
+      <c r="P125" s="16"/>
+      <c r="Q125" s="16"/>
+      <c r="R125" s="16"/>
+      <c r="S125" s="12"/>
     </row>
     <row r="126" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A126" s="10"/>
-      <c r="B126" s="10"/>
-      <c r="C126" s="10"/>
-      <c r="D126" s="10"/>
-      <c r="E126" s="10"/>
-      <c r="F126" s="14"/>
+      <c r="A126" s="9"/>
+      <c r="B126" s="9"/>
+      <c r="C126" s="9"/>
+      <c r="D126" s="9"/>
+      <c r="E126" s="9"/>
+      <c r="F126" s="13"/>
       <c r="G126" s="3"/>
-      <c r="H126" s="10"/>
+      <c r="H126" s="9"/>
       <c r="I126" s="3"/>
-      <c r="J126" s="10"/>
-      <c r="K126" s="10"/>
-      <c r="L126" s="10"/>
-      <c r="M126" s="10"/>
-      <c r="N126" s="10"/>
+      <c r="J126" s="9"/>
+      <c r="K126" s="9"/>
+      <c r="L126" s="9"/>
+      <c r="M126" s="9"/>
+      <c r="N126" s="9"/>
       <c r="O126" s="3"/>
-      <c r="P126" s="17"/>
-      <c r="Q126" s="17"/>
-      <c r="R126" s="17"/>
-      <c r="S126" s="13"/>
+      <c r="P126" s="16"/>
+      <c r="Q126" s="16"/>
+      <c r="R126" s="16"/>
+      <c r="S126" s="12"/>
     </row>
     <row r="127" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A127" s="10"/>
-      <c r="B127" s="10"/>
-      <c r="C127" s="10"/>
-      <c r="D127" s="10"/>
-      <c r="E127" s="10"/>
-      <c r="F127" s="14"/>
+      <c r="A127" s="9"/>
+      <c r="B127" s="9"/>
+      <c r="C127" s="9"/>
+      <c r="D127" s="9"/>
+      <c r="E127" s="9"/>
+      <c r="F127" s="13"/>
       <c r="G127" s="3"/>
-      <c r="H127" s="10"/>
+      <c r="H127" s="9"/>
       <c r="I127" s="3"/>
-      <c r="J127" s="10"/>
-      <c r="K127" s="10"/>
-      <c r="L127" s="10"/>
-      <c r="M127" s="10"/>
-      <c r="N127" s="10"/>
+      <c r="J127" s="9"/>
+      <c r="K127" s="9"/>
+      <c r="L127" s="9"/>
+      <c r="M127" s="9"/>
+      <c r="N127" s="9"/>
       <c r="O127" s="3"/>
-      <c r="P127" s="17"/>
-      <c r="Q127" s="17"/>
-      <c r="R127" s="17"/>
-      <c r="S127" s="13"/>
+      <c r="P127" s="16"/>
+      <c r="Q127" s="16"/>
+      <c r="R127" s="16"/>
+      <c r="S127" s="12"/>
     </row>
     <row r="128" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A128" s="10"/>
-      <c r="B128" s="10"/>
-      <c r="C128" s="10"/>
-      <c r="D128" s="10"/>
-      <c r="E128" s="10"/>
-      <c r="F128" s="14"/>
+      <c r="A128" s="9"/>
+      <c r="B128" s="9"/>
+      <c r="C128" s="9"/>
+      <c r="D128" s="9"/>
+      <c r="E128" s="9"/>
+      <c r="F128" s="13"/>
       <c r="G128" s="3"/>
-      <c r="H128" s="10"/>
+      <c r="H128" s="9"/>
       <c r="I128" s="3"/>
-      <c r="J128" s="10"/>
-      <c r="K128" s="10"/>
-      <c r="L128" s="10"/>
-      <c r="M128" s="10"/>
-      <c r="N128" s="10"/>
+      <c r="J128" s="9"/>
+      <c r="K128" s="9"/>
+      <c r="L128" s="9"/>
+      <c r="M128" s="9"/>
+      <c r="N128" s="9"/>
       <c r="O128" s="3"/>
-      <c r="P128" s="17"/>
-      <c r="Q128" s="17"/>
-      <c r="R128" s="17"/>
-      <c r="S128" s="13"/>
+      <c r="P128" s="16"/>
+      <c r="Q128" s="16"/>
+      <c r="R128" s="16"/>
+      <c r="S128" s="12"/>
     </row>
     <row r="129" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A129" s="10"/>
-      <c r="B129" s="10"/>
-      <c r="C129" s="10"/>
-      <c r="D129" s="10"/>
-      <c r="E129" s="10"/>
-      <c r="F129" s="14"/>
+      <c r="A129" s="9"/>
+      <c r="B129" s="9"/>
+      <c r="C129" s="9"/>
+      <c r="D129" s="9"/>
+      <c r="E129" s="9"/>
+      <c r="F129" s="13"/>
       <c r="G129" s="3"/>
-      <c r="H129" s="10"/>
+      <c r="H129" s="9"/>
       <c r="I129" s="3"/>
-      <c r="J129" s="10"/>
-      <c r="K129" s="10"/>
-      <c r="L129" s="10"/>
-      <c r="M129" s="10"/>
-      <c r="N129" s="10"/>
+      <c r="J129" s="9"/>
+      <c r="K129" s="9"/>
+      <c r="L129" s="9"/>
+      <c r="M129" s="9"/>
+      <c r="N129" s="9"/>
       <c r="O129" s="3"/>
-      <c r="P129" s="17"/>
-      <c r="Q129" s="17"/>
-      <c r="R129" s="17"/>
-      <c r="S129" s="13"/>
+      <c r="P129" s="16"/>
+      <c r="Q129" s="16"/>
+      <c r="R129" s="16"/>
+      <c r="S129" s="12"/>
     </row>
     <row r="130" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A130" s="6"/>
-      <c r="J130" s="6"/>
-      <c r="K130" s="6"/>
-      <c r="L130" s="6"/>
-      <c r="M130" s="6"/>
-      <c r="N130" s="6"/>
-      <c r="P130" s="18"/>
-      <c r="Q130" s="18"/>
-      <c r="R130" s="18"/>
+      <c r="J130" s="2"/>
+      <c r="K130" s="2"/>
+      <c r="L130" s="2"/>
+      <c r="M130" s="2"/>
+      <c r="N130" s="2"/>
+      <c r="P130" s="17"/>
+      <c r="Q130" s="17"/>
+      <c r="R130" s="17"/>
     </row>
     <row r="131" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A131" s="6"/>
-      <c r="J131" s="6"/>
-      <c r="K131" s="6"/>
-      <c r="L131" s="6"/>
-      <c r="M131" s="6"/>
-      <c r="N131" s="6"/>
-      <c r="P131" s="18"/>
-      <c r="Q131" s="18"/>
-      <c r="R131" s="18"/>
+      <c r="J131" s="2"/>
+      <c r="K131" s="2"/>
+      <c r="L131" s="2"/>
+      <c r="M131" s="2"/>
+      <c r="N131" s="2"/>
+      <c r="P131" s="17"/>
+      <c r="Q131" s="17"/>
+      <c r="R131" s="17"/>
     </row>
     <row r="132" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A132" s="6"/>
-      <c r="J132" s="6"/>
-      <c r="K132" s="6"/>
-      <c r="L132" s="6"/>
-      <c r="M132" s="6"/>
-      <c r="N132" s="6"/>
-      <c r="P132" s="18"/>
-      <c r="Q132" s="18"/>
-      <c r="R132" s="18"/>
+      <c r="J132" s="2"/>
+      <c r="K132" s="2"/>
+      <c r="L132" s="2"/>
+      <c r="M132" s="2"/>
+      <c r="N132" s="2"/>
+      <c r="P132" s="17"/>
+      <c r="Q132" s="17"/>
+      <c r="R132" s="17"/>
     </row>
     <row r="133" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A133" s="6"/>
-      <c r="J133" s="6"/>
-      <c r="K133" s="6"/>
-      <c r="L133" s="6"/>
-      <c r="M133" s="6"/>
-      <c r="N133" s="6"/>
-      <c r="P133" s="18"/>
-      <c r="Q133" s="18"/>
-      <c r="R133" s="18"/>
+      <c r="J133" s="2"/>
+      <c r="K133" s="2"/>
+      <c r="L133" s="2"/>
+      <c r="M133" s="2"/>
+      <c r="N133" s="2"/>
+      <c r="P133" s="17"/>
+      <c r="Q133" s="17"/>
+      <c r="R133" s="17"/>
     </row>
     <row r="134" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A134" s="6"/>
-      <c r="J134" s="6"/>
-      <c r="K134" s="6"/>
-      <c r="L134" s="6"/>
-      <c r="M134" s="6"/>
-      <c r="N134" s="6"/>
-      <c r="P134" s="18"/>
-      <c r="Q134" s="18"/>
-      <c r="R134" s="18"/>
+      <c r="J134" s="2"/>
+      <c r="K134" s="2"/>
+      <c r="L134" s="2"/>
+      <c r="M134" s="2"/>
+      <c r="N134" s="2"/>
+      <c r="P134" s="17"/>
+      <c r="Q134" s="17"/>
+      <c r="R134" s="17"/>
     </row>
     <row r="135" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A135" s="6"/>
-      <c r="J135" s="6"/>
-      <c r="K135" s="6"/>
-      <c r="L135" s="6"/>
-      <c r="M135" s="6"/>
-      <c r="N135" s="6"/>
-      <c r="P135" s="18"/>
-      <c r="Q135" s="18"/>
-      <c r="R135" s="18"/>
+      <c r="J135" s="2"/>
+      <c r="K135" s="2"/>
+      <c r="L135" s="2"/>
+      <c r="M135" s="2"/>
+      <c r="N135" s="2"/>
+      <c r="P135" s="17"/>
+      <c r="Q135" s="17"/>
+      <c r="R135" s="17"/>
     </row>
     <row r="136" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A136" s="6"/>
-      <c r="J136" s="6"/>
-      <c r="K136" s="6"/>
-      <c r="L136" s="6"/>
-      <c r="M136" s="6"/>
-      <c r="N136" s="6"/>
-      <c r="P136" s="18"/>
-      <c r="Q136" s="18"/>
-      <c r="R136" s="18"/>
+      <c r="J136" s="2"/>
+      <c r="K136" s="2"/>
+      <c r="L136" s="2"/>
+      <c r="M136" s="2"/>
+      <c r="N136" s="2"/>
+      <c r="P136" s="17"/>
+      <c r="Q136" s="17"/>
+      <c r="R136" s="17"/>
     </row>
     <row r="137" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A137" s="6"/>
-      <c r="J137" s="6"/>
-      <c r="K137" s="6"/>
-      <c r="L137" s="6"/>
-      <c r="M137" s="6"/>
-      <c r="N137" s="6"/>
-      <c r="P137" s="18"/>
-      <c r="Q137" s="18"/>
-      <c r="R137" s="18"/>
+      <c r="J137" s="2"/>
+      <c r="K137" s="2"/>
+      <c r="L137" s="2"/>
+      <c r="M137" s="2"/>
+      <c r="N137" s="2"/>
+      <c r="P137" s="17"/>
+      <c r="Q137" s="17"/>
+      <c r="R137" s="17"/>
     </row>
     <row r="138" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A138" s="6"/>
-      <c r="J138" s="6"/>
-      <c r="K138" s="6"/>
-      <c r="L138" s="6"/>
-      <c r="M138" s="6"/>
-      <c r="N138" s="6"/>
-      <c r="P138" s="18"/>
-      <c r="Q138" s="18"/>
-      <c r="R138" s="18"/>
+      <c r="J138" s="2"/>
+      <c r="K138" s="2"/>
+      <c r="L138" s="2"/>
+      <c r="M138" s="2"/>
+      <c r="N138" s="2"/>
+      <c r="P138" s="17"/>
+      <c r="Q138" s="17"/>
+      <c r="R138" s="17"/>
     </row>
     <row r="139" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A139" s="6"/>
-      <c r="J139" s="6"/>
-      <c r="K139" s="6"/>
-      <c r="L139" s="6"/>
-      <c r="M139" s="6"/>
-      <c r="N139" s="6"/>
-      <c r="P139" s="18"/>
-      <c r="Q139" s="18"/>
-      <c r="R139" s="18"/>
+      <c r="J139" s="2"/>
+      <c r="K139" s="2"/>
+      <c r="L139" s="2"/>
+      <c r="M139" s="2"/>
+      <c r="N139" s="2"/>
+      <c r="P139" s="17"/>
+      <c r="Q139" s="17"/>
+      <c r="R139" s="17"/>
     </row>
     <row r="1048575" spans="16:16" x14ac:dyDescent="0.3">
-      <c r="P1048575" s="20"/>
+      <c r="P1048575" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="85">
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="D49:D52"/>
+    <mergeCell ref="C49:C52"/>
+    <mergeCell ref="B49:B52"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="D35:D44"/>
+    <mergeCell ref="C35:C44"/>
+    <mergeCell ref="B35:B44"/>
+    <mergeCell ref="D45:D48"/>
+    <mergeCell ref="C45:C48"/>
+    <mergeCell ref="B45:B48"/>
+    <mergeCell ref="B73:B75"/>
+    <mergeCell ref="C73:C75"/>
+    <mergeCell ref="D73:D75"/>
+    <mergeCell ref="D71:D72"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="B17:B21"/>
+    <mergeCell ref="C17:C21"/>
+    <mergeCell ref="D17:D21"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="B25:B28"/>
+    <mergeCell ref="C25:C28"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="B80:B84"/>
+    <mergeCell ref="C80:C84"/>
+    <mergeCell ref="D80:D84"/>
+    <mergeCell ref="B76:B79"/>
+    <mergeCell ref="C76:C79"/>
+    <mergeCell ref="D76:D79"/>
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="D69:D70"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="C71:C72"/>
+    <mergeCell ref="B62:B64"/>
+    <mergeCell ref="C62:C64"/>
+    <mergeCell ref="D62:D64"/>
+    <mergeCell ref="B65:B68"/>
+    <mergeCell ref="C65:C68"/>
+    <mergeCell ref="D65:D68"/>
+    <mergeCell ref="B53:B57"/>
+    <mergeCell ref="C53:C57"/>
+    <mergeCell ref="D53:D57"/>
+    <mergeCell ref="B58:B61"/>
+    <mergeCell ref="C58:C61"/>
+    <mergeCell ref="D58:D61"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="D25:D28"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
     <mergeCell ref="P2:P3"/>
     <mergeCell ref="Q2:Q3"/>
     <mergeCell ref="R2:R3"/>
@@ -8363,75 +8408,6 @@
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="O2:O3"/>
     <mergeCell ref="J2:N2"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="D25:D28"/>
-    <mergeCell ref="B53:B57"/>
-    <mergeCell ref="C53:C57"/>
-    <mergeCell ref="D53:D57"/>
-    <mergeCell ref="B58:B61"/>
-    <mergeCell ref="C58:C61"/>
-    <mergeCell ref="D58:D61"/>
-    <mergeCell ref="C69:C70"/>
-    <mergeCell ref="D69:D70"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="C71:C72"/>
-    <mergeCell ref="B62:B64"/>
-    <mergeCell ref="C62:C64"/>
-    <mergeCell ref="D62:D64"/>
-    <mergeCell ref="B65:B68"/>
-    <mergeCell ref="C65:C68"/>
-    <mergeCell ref="D65:D68"/>
-    <mergeCell ref="B80:B84"/>
-    <mergeCell ref="C80:C84"/>
-    <mergeCell ref="D80:D84"/>
-    <mergeCell ref="B76:B79"/>
-    <mergeCell ref="C76:C79"/>
-    <mergeCell ref="D76:D79"/>
-    <mergeCell ref="B73:B75"/>
-    <mergeCell ref="C73:C75"/>
-    <mergeCell ref="D73:D75"/>
-    <mergeCell ref="D71:D72"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="B17:B21"/>
-    <mergeCell ref="C17:C21"/>
-    <mergeCell ref="D17:D21"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="B25:B28"/>
-    <mergeCell ref="C25:C28"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="D49:D52"/>
-    <mergeCell ref="C49:C52"/>
-    <mergeCell ref="B49:B52"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="D35:D44"/>
-    <mergeCell ref="C35:C44"/>
-    <mergeCell ref="B35:B44"/>
-    <mergeCell ref="D45:D48"/>
-    <mergeCell ref="C45:C48"/>
-    <mergeCell ref="B45:B48"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8451,16 +8427,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="11"/>
+      <c r="D1" s="10"/>
     </row>
     <row r="2" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -8619,16 +8595,16 @@
       <c r="D14" s="3"/>
     </row>
     <row r="15" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="6" t="s">
         <v>576</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="6" t="s">
         <v>577</v>
       </c>
-      <c r="D15" s="7"/>
+      <c r="D15" s="6"/>
     </row>
     <row r="16" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
@@ -8649,16 +8625,16 @@
       <c r="D17" s="3"/>
     </row>
     <row r="18" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="10" t="s">
         <v>28</v>
       </c>
     </row>
